--- a/Ground Truth/ground_truth_appliance.xlsx
+++ b/Ground Truth/ground_truth_appliance.xlsx
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="L2" t="n">
         <v>0.95</v>
@@ -564,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9585</v>
+        <v>0.9615</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0774</v>
+        <v>0.082</v>
       </c>
       <c r="R2" t="n">
         <v>0.468</v>
@@ -632,13 +632,13 @@
         <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8294999999999999</v>
+        <v>0.8295</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0396</v>
+        <v>0.0421</v>
       </c>
       <c r="R3" t="n">
         <v>0.468</v>
@@ -700,13 +700,13 @@
         <v>0.43</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0396</v>
+        <v>0.0421</v>
       </c>
       <c r="R4" t="n">
         <v>0.439</v>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="L5" t="n">
         <v>0.09</v>
@@ -768,13 +768,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4505</v>
+        <v>0.4385</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5504</v>
+        <v>0.6312</v>
       </c>
       <c r="R5" t="n">
         <v>3.331</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="L6" t="n">
         <v>0.15</v>
@@ -836,13 +836,13 @@
         <v>0.57</v>
       </c>
       <c r="O6" t="n">
-        <v>0.429</v>
+        <v>0.453</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2816</v>
+        <v>0.2447</v>
       </c>
       <c r="R6" t="n">
         <v>3.123</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="L7" t="n">
         <v>0.09</v>
@@ -904,13 +904,13 @@
         <v>0.6</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3365</v>
+        <v>0.3245</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5504</v>
+        <v>0.6312</v>
       </c>
       <c r="R7" t="n">
         <v>3.331</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="L8" t="n">
         <v>0.6899999999999999</v>
@@ -972,13 +972,13 @@
         <v>0.93</v>
       </c>
       <c r="O8" t="n">
-        <v>0.839</v>
+        <v>0.854</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1188</v>
+        <v>0.0931</v>
       </c>
       <c r="R8" t="n">
         <v>1.318</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="L9" t="n">
         <v>0.67</v>
@@ -1040,13 +1040,13 @@
         <v>0.41</v>
       </c>
       <c r="O9" t="n">
-        <v>0.62</v>
+        <v>0.623</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2322</v>
+        <v>0.246</v>
       </c>
       <c r="R9" t="n">
         <v>1.405</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="L10" t="n">
         <v>0.67</v>
@@ -1108,13 +1108,13 @@
         <v>0.41</v>
       </c>
       <c r="O10" t="n">
-        <v>0.668</v>
+        <v>0.671</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1188</v>
+        <v>0.1262</v>
       </c>
       <c r="R10" t="n">
         <v>1.405</v>
@@ -1176,13 +1176,13 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0246</v>
+        <v>0.0262</v>
       </c>
       <c r="R11" t="n">
         <v>0.291</v>
@@ -1250,7 +1250,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0482</v>
+        <v>0.051</v>
       </c>
       <c r="R12" t="n">
         <v>0.291</v>
@@ -1312,13 +1312,13 @@
         <v>0.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7184999999999999</v>
+        <v>0.7185</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0246</v>
+        <v>0.0262</v>
       </c>
       <c r="R13" t="n">
         <v>0.291</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>It's just past 5 PM, when should I run the dryer?</t>
+          <t>It's just past 5 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1380,13 +1380,13 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.398</v>
+        <v>0.404</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.602</v>
+        <v>0.6379</v>
       </c>
       <c r="R14" t="n">
         <v>3.643</v>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>It's just past 5 PM, when should I run the dryer?</t>
+          <t>It's just past 5 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1448,13 +1448,13 @@
         <v>0.78</v>
       </c>
       <c r="O15" t="n">
-        <v>0.337</v>
+        <v>0.343</v>
       </c>
       <c r="P15" t="n">
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.602</v>
+        <v>0.6379</v>
       </c>
       <c r="R15" t="n">
         <v>3.643</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>It's just past 5 PM, when should I run the dryer?</t>
+          <t>It's just past 5 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="L16" t="n">
         <v>0.07000000000000001</v>
@@ -1516,13 +1516,13 @@
         <v>0.52</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3835</v>
+        <v>0.4195</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.308</v>
+        <v>0.2413</v>
       </c>
       <c r="R16" t="n">
         <v>3.416</v>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L17" t="n">
         <v>0.9</v>
@@ -1584,13 +1584,13 @@
         <v>0.85</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8835</v>
+        <v>0.8925</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0572</v>
+        <v>0.0448</v>
       </c>
       <c r="R17" t="n">
         <v>0.634</v>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L18" t="n">
         <v>0.88</v>
@@ -1652,13 +1652,13 @@
         <v>0.35</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7494999999999999</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0572</v>
+        <v>0.0608</v>
       </c>
       <c r="R18" t="n">
         <v>0.677</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="L19" t="n">
         <v>0.88</v>
@@ -1720,13 +1720,13 @@
         <v>0.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.677</v>
+        <v>0.68</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1118</v>
+        <v>0.1185</v>
       </c>
       <c r="R19" t="n">
         <v>0.677</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="L20" t="n">
         <v>0.22</v>
@@ -1788,13 +1788,13 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.526</v>
+        <v>0.517</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4816</v>
+        <v>0.5523</v>
       </c>
       <c r="R20" t="n">
         <v>2.915</v>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="L21" t="n">
         <v>0.22</v>
@@ -1856,13 +1856,13 @@
         <v>0.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4119999999999999</v>
+        <v>0.403</v>
       </c>
       <c r="P21" t="n">
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4816</v>
+        <v>0.5523</v>
       </c>
       <c r="R21" t="n">
         <v>2.915</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="L22" t="n">
         <v>0.27</v>
@@ -1924,13 +1924,13 @@
         <v>0.31</v>
       </c>
       <c r="O22" t="n">
-        <v>0.413</v>
+        <v>0.434</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2464</v>
+        <v>0.2141</v>
       </c>
       <c r="R22" t="n">
         <v>2.733</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the dishwasher. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the dishwasher. When should I run it?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1998,7 +1998,7 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2842</v>
+        <v>0.3097</v>
       </c>
       <c r="R23" t="n">
         <v>1.457</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the dishwasher. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the dishwasher. When should I run it?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2060,13 +2060,13 @@
         <v>0.92</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7414999999999999</v>
+        <v>0.7415</v>
       </c>
       <c r="P24" t="n">
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2842</v>
+        <v>0.3097</v>
       </c>
       <c r="R24" t="n">
         <v>1.457</v>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the dishwasher. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the dishwasher. When should I run it?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="L25" t="n">
         <v>0.68</v>
@@ -2128,13 +2128,13 @@
         <v>0.29</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6445</v>
+        <v>0.6625</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.14</v>
+        <v>0.1128</v>
       </c>
       <c r="R25" t="n">
         <v>1.366</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2202,7 +2202,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.96</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="R26" t="n">
         <v>3.123</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2264,13 +2264,13 @@
         <v>0.26</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3804999999999999</v>
+        <v>0.3805</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.228</v>
+        <v>0.2515</v>
       </c>
       <c r="R27" t="n">
         <v>2.928</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2332,13 +2332,13 @@
         <v>0.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0.4984999999999999</v>
+        <v>0.4985</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.228</v>
+        <v>0.2515</v>
       </c>
       <c r="R28" t="n">
         <v>3.123</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>It's around 7 in the evening, when should I run the dishwasher?</t>
+          <t>It's around 7 in the evening. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2400,13 +2400,13 @@
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9055000000000001</v>
+        <v>0.9055</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0722</v>
+        <v>0.0796</v>
       </c>
       <c r="R29" t="n">
         <v>0.989</v>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>It's around 7 in the evening, when should I run the dishwasher?</t>
+          <t>It's around 7 in the evening. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="L30" t="n">
         <v>0.79</v>
@@ -2468,13 +2468,13 @@
         <v>0.83</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7579999999999999</v>
+        <v>0.767</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.304</v>
+        <v>0.3111</v>
       </c>
       <c r="R30" t="n">
         <v>0.989</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>It's around 7 in the evening, when should I run the dishwasher?</t>
+          <t>It's around 7 in the evening. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="L31" t="n">
         <v>0.79</v>
@@ -2536,13 +2536,13 @@
         <v>0.76</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7374999999999999</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="P31" t="n">
         <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.304</v>
+        <v>0.3111</v>
       </c>
       <c r="R31" t="n">
         <v>0.989</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="L32" t="n">
         <v>0.79</v>
@@ -2604,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8845</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="L33" t="n">
         <v>0.79</v>
@@ -2672,7 +2672,7 @@
         <v>0.76</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8155</v>
+        <v>0.8185</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="L34" t="n">
         <v>0.8100000000000001</v>
@@ -2740,7 +2740,7 @@
         <v>0.43</v>
       </c>
       <c r="O34" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the washing machine. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the washing machine. When should I run it?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="L35" t="n">
         <v>0.97</v>
@@ -2808,13 +2808,13 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9474999999999999</v>
+        <v>0.9505</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1216</v>
+        <v>0.1244</v>
       </c>
       <c r="R35" t="n">
         <v>0.396</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the washing machine. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the washing machine. When should I run it?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2882,7 +2882,7 @@
         <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0289</v>
+        <v>0.0319</v>
       </c>
       <c r="R36" t="n">
         <v>0.396</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the washing machine. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the washing machine. When should I run it?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0.98</v>
@@ -2944,13 +2944,13 @@
         <v>0.15</v>
       </c>
       <c r="O37" t="n">
-        <v>0.6804999999999999</v>
+        <v>0.6835</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.0289</v>
+        <v>0.023</v>
       </c>
       <c r="R37" t="n">
         <v>0.371</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="L38" t="n">
         <v>0.07000000000000001</v>
@@ -3012,13 +3012,13 @@
         <v>0.85</v>
       </c>
       <c r="O38" t="n">
-        <v>0.513</v>
+        <v>0.543</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.266</v>
+        <v>0.2121</v>
       </c>
       <c r="R38" t="n">
         <v>3.416</v>
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.12</v>
+        <v>1.1461</v>
       </c>
       <c r="R39" t="n">
         <v>3.643</v>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="L40" t="n">
         <v>0.07000000000000001</v>
@@ -3148,13 +3148,13 @@
         <v>0.74</v>
       </c>
       <c r="O40" t="n">
-        <v>0.4705</v>
+        <v>0.4675</v>
       </c>
       <c r="P40" t="n">
         <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.266</v>
+        <v>0.2934</v>
       </c>
       <c r="R40" t="n">
         <v>3.416</v>
@@ -3222,7 +3222,7 @@
         <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.024</v>
+        <v>1.0479</v>
       </c>
       <c r="R41" t="n">
         <v>3.331</v>
@@ -3290,7 +3290,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.2432</v>
+        <v>0.2682</v>
       </c>
       <c r="R42" t="n">
         <v>3.331</v>
@@ -3352,13 +3352,13 @@
         <v>0.49</v>
       </c>
       <c r="O43" t="n">
-        <v>0.4350000000000001</v>
+        <v>0.435</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.2432</v>
+        <v>0.2682</v>
       </c>
       <c r="R43" t="n">
         <v>3.331</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="L44" t="n">
         <v>0.79</v>
@@ -3420,13 +3420,13 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.8604999999999999</v>
+        <v>0.8635</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.1757</v>
+        <v>0.1874</v>
       </c>
       <c r="R44" t="n">
         <v>0.989</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="L45" t="n">
         <v>0.79</v>
@@ -3488,13 +3488,13 @@
         <v>0.75</v>
       </c>
       <c r="O45" t="n">
-        <v>0.7889999999999999</v>
+        <v>0.792</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.1757</v>
+        <v>0.1874</v>
       </c>
       <c r="R45" t="n">
         <v>0.989</v>
@@ -3562,7 +3562,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.0883</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="R46" t="n">
         <v>0.989</v>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -3624,7 +3624,7 @@
         <v>0.93</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9645000000000001</v>
+        <v>0.9675</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
@@ -3692,7 +3692,7 @@
         <v>0.35</v>
       </c>
       <c r="O48" t="n">
-        <v>0.8035</v>
+        <v>0.8065</v>
       </c>
       <c r="P48" t="n">
         <v>3</v>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>
@@ -3760,7 +3760,7 @@
         <v>0.51</v>
       </c>
       <c r="O49" t="n">
-        <v>0.8535</v>
+        <v>0.8565</v>
       </c>
       <c r="P49" t="n">
         <v>2</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>It's just past 5 PM, when should I run the washer?</t>
+          <t>It's just past 5 PM. When should I run the washer?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L50" t="n">
         <v>0.97</v>
@@ -3828,13 +3828,13 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9685</v>
+        <v>0.9715</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0703</v>
+        <v>0.075</v>
       </c>
       <c r="R50" t="n">
         <v>0.396</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>It's just past 5 PM, when should I run the washer?</t>
+          <t>It's just past 5 PM. When should I run the washer?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L51" t="n">
         <v>0.97</v>
@@ -3896,13 +3896,13 @@
         <v>0.76</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9005000000000001</v>
+        <v>0.9035</v>
       </c>
       <c r="P51" t="n">
         <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.0703</v>
+        <v>0.075</v>
       </c>
       <c r="R51" t="n">
         <v>0.396</v>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>It's just past 5 PM, when should I run the washer?</t>
+          <t>It's just past 5 PM. When should I run the washer?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L52" t="n">
         <v>0.97</v>
@@ -3964,13 +3964,13 @@
         <v>0.68</v>
       </c>
       <c r="O52" t="n">
-        <v>0.8935</v>
+        <v>0.8965</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.0353</v>
+        <v>0.0379</v>
       </c>
       <c r="R52" t="n">
         <v>0.396</v>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -4032,13 +4032,13 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.377</v>
+        <v>0.383</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.6475</v>
+        <v>0.6904</v>
       </c>
       <c r="R53" t="n">
         <v>3.643</v>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="L54" t="n">
         <v>0.07000000000000001</v>
@@ -4100,13 +4100,13 @@
         <v>0.15</v>
       </c>
       <c r="O54" t="n">
-        <v>0.291</v>
+        <v>0.327</v>
       </c>
       <c r="P54" t="n">
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.3255</v>
+        <v>0.2677</v>
       </c>
       <c r="R54" t="n">
         <v>3.416</v>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -4168,13 +4168,13 @@
         <v>0.43</v>
       </c>
       <c r="O55" t="n">
-        <v>0.3365</v>
+        <v>0.3395</v>
       </c>
       <c r="P55" t="n">
         <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.3255</v>
+        <v>0.3487</v>
       </c>
       <c r="R55" t="n">
         <v>3.643</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I'm trying to figure out when to start the washing machine. When should I run it?</t>
+          <t>It's late afternoon, around 4, and I'm trying to figure out when to start the washing machine. When should I run it?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4236,13 +4236,13 @@
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.9879999999999999</v>
+        <v>0.988</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.0518</v>
+        <v>0.0552</v>
       </c>
       <c r="R56" t="n">
         <v>0.291</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I'm trying to figure out when to start the washing machine. When should I run it?</t>
+          <t>It's late afternoon, around 4, and I'm trying to figure out when to start the washing machine. When should I run it?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4304,13 +4304,13 @@
         <v>0.68</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9099999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="P57" t="n">
         <v>2</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.026</v>
+        <v>0.0279</v>
       </c>
       <c r="R57" t="n">
         <v>0.291</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I'm trying to figure out when to start the washing machine. When should I run it?</t>
+          <t>It's late afternoon, around 4, and I'm trying to figure out when to start the washing machine. When should I run it?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4372,13 +4372,13 @@
         <v>0.62</v>
       </c>
       <c r="O58" t="n">
-        <v>0.8909999999999999</v>
+        <v>0.891</v>
       </c>
       <c r="P58" t="n">
         <v>3</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.026</v>
+        <v>0.0279</v>
       </c>
       <c r="R58" t="n">
         <v>0.291</v>
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="L59" t="n">
         <v>0.79</v>
@@ -4440,13 +4440,13 @@
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.8515</v>
+        <v>0.8545</v>
       </c>
       <c r="P59" t="n">
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.1928</v>
+        <v>0.2101</v>
       </c>
       <c r="R59" t="n">
         <v>0.989</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="L60" t="n">
         <v>0.8100000000000001</v>
@@ -4508,13 +4508,13 @@
         <v>0.29</v>
       </c>
       <c r="O60" t="n">
-        <v>0.731</v>
+        <v>0.74</v>
       </c>
       <c r="P60" t="n">
         <v>3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.095</v>
+        <v>0.0765</v>
       </c>
       <c r="R60" t="n">
         <v>0.927</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="L61" t="n">
         <v>0.79</v>
@@ -4576,13 +4576,13 @@
         <v>0.85</v>
       </c>
       <c r="O61" t="n">
-        <v>0.8109999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="P61" t="n">
         <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.1928</v>
+        <v>0.2101</v>
       </c>
       <c r="R61" t="n">
         <v>0.989</v>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="L62" t="n">
         <v>0.97</v>
@@ -4644,13 +4644,13 @@
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.9654999999999999</v>
+        <v>0.9805</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.0771</v>
+        <v>0.0531</v>
       </c>
       <c r="R62" t="n">
         <v>0.396</v>
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="L63" t="n">
         <v>0.97</v>
@@ -4712,13 +4712,13 @@
         <v>0.62</v>
       </c>
       <c r="O63" t="n">
-        <v>0.8564999999999999</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="P63" t="n">
         <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.0771</v>
+        <v>0.0456</v>
       </c>
       <c r="R63" t="n">
         <v>0.396</v>
@@ -4786,7 +4786,7 @@
         <v>3</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.038</v>
+        <v>0.0456</v>
       </c>
       <c r="R64" t="n">
         <v>0.371</v>
@@ -4854,7 +4854,7 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.7105</v>
+        <v>0.7741</v>
       </c>
       <c r="R65" t="n">
         <v>3.643</v>
@@ -4922,7 +4922,7 @@
         <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.35</v>
+        <v>0.381</v>
       </c>
       <c r="R66" t="n">
         <v>3.643</v>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="L67" t="n">
         <v>0.07000000000000001</v>
@@ -4984,13 +4984,13 @@
         <v>0.15</v>
       </c>
       <c r="O67" t="n">
-        <v>0.256</v>
+        <v>0.295</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.35</v>
+        <v>0.282</v>
       </c>
       <c r="R67" t="n">
         <v>3.416</v>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5058,7 +5058,7 @@
         <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.12</v>
+        <v>1.1461</v>
       </c>
       <c r="R68" t="n">
         <v>3.643</v>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="L69" t="n">
         <v>0.07000000000000001</v>
@@ -5120,13 +5120,13 @@
         <v>0.37</v>
       </c>
       <c r="O69" t="n">
-        <v>0.337</v>
+        <v>0.334</v>
       </c>
       <c r="P69" t="n">
         <v>3</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.266</v>
+        <v>0.2934</v>
       </c>
       <c r="R69" t="n">
         <v>3.416</v>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -5188,13 +5188,13 @@
         <v>0.49</v>
       </c>
       <c r="O70" t="n">
-        <v>0.3945</v>
+        <v>0.3915</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.266</v>
+        <v>0.2934</v>
       </c>
       <c r="R70" t="n">
         <v>3.643</v>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="L71" t="n">
         <v>0.79</v>
@@ -5256,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8845</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="L72" t="n">
         <v>0.8100000000000001</v>
@@ -5324,7 +5324,7 @@
         <v>0.15</v>
       </c>
       <c r="O72" t="n">
-        <v>0.6669999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="P72" t="n">
         <v>3</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="L73" t="n">
         <v>0.8100000000000001</v>
@@ -5392,7 +5392,7 @@
         <v>0.29</v>
       </c>
       <c r="O73" t="n">
-        <v>0.696</v>
+        <v>0.699</v>
       </c>
       <c r="P73" t="n">
         <v>2</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>It's past 1 in the morning, when should I run the dryer?</t>
+          <t>It's past 1 in the morning. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="L74" t="n">
         <v>0.74</v>
@@ -5460,7 +5460,7 @@
         <v>0.85</v>
       </c>
       <c r="O74" t="n">
-        <v>0.7925</v>
+        <v>0.7985</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>It's past 1 in the morning, when should I run the dryer?</t>
+          <t>It's past 1 in the morning. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="L75" t="n">
         <v>0.71</v>
@@ -5528,7 +5528,7 @@
         <v>0.3</v>
       </c>
       <c r="O75" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6335</v>
       </c>
       <c r="P75" t="n">
         <v>3</v>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>It's past 1 in the morning, when should I run the dryer?</t>
+          <t>It's past 1 in the morning. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="L76" t="n">
         <v>0.71</v>
@@ -5596,7 +5596,7 @@
         <v>0.6</v>
       </c>
       <c r="O76" t="n">
-        <v>0.7244999999999999</v>
+        <v>0.7305</v>
       </c>
       <c r="P76" t="n">
         <v>2</v>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="L77" t="n">
         <v>0.97</v>
@@ -5664,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.9774999999999999</v>
+        <v>0.9805</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="L78" t="n">
         <v>0.97</v>
@@ -5732,7 +5732,7 @@
         <v>0.34</v>
       </c>
       <c r="O78" t="n">
-        <v>0.7805</v>
+        <v>0.7835</v>
       </c>
       <c r="P78" t="n">
         <v>3</v>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="L79" t="n">
         <v>0.97</v>
@@ -5800,7 +5800,7 @@
         <v>0.68</v>
       </c>
       <c r="O79" t="n">
-        <v>0.8875</v>
+        <v>0.8905</v>
       </c>
       <c r="P79" t="n">
         <v>2</v>
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="L80" t="n">
         <v>0.07000000000000001</v>
@@ -5868,13 +5868,13 @@
         <v>0.85</v>
       </c>
       <c r="O80" t="n">
-        <v>0.513</v>
+        <v>0.543</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.266</v>
+        <v>0.2121</v>
       </c>
       <c r="R80" t="n">
         <v>3.416</v>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -5936,13 +5936,13 @@
         <v>0.67</v>
       </c>
       <c r="O81" t="n">
-        <v>0.4515</v>
+        <v>0.4485</v>
       </c>
       <c r="P81" t="n">
         <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.266</v>
+        <v>0.2934</v>
       </c>
       <c r="R81" t="n">
         <v>3.643</v>
@@ -6010,7 +6010,7 @@
         <v>3</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.12</v>
+        <v>1.1461</v>
       </c>
       <c r="R82" t="n">
         <v>3.643</v>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="L83" t="n">
         <v>0.07000000000000001</v>
@@ -6072,13 +6072,13 @@
         <v>0.85</v>
       </c>
       <c r="O83" t="n">
-        <v>0.476</v>
+        <v>0.512</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.3255</v>
+        <v>0.2677</v>
       </c>
       <c r="R83" t="n">
         <v>3.416</v>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -6140,13 +6140,13 @@
         <v>0.6</v>
       </c>
       <c r="O84" t="n">
-        <v>0.263</v>
+        <v>0.269</v>
       </c>
       <c r="P84" t="n">
         <v>2</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.6475</v>
+        <v>0.6904</v>
       </c>
       <c r="R84" t="n">
         <v>3.643</v>
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -6208,13 +6208,13 @@
         <v>0.39</v>
       </c>
       <c r="O85" t="n">
-        <v>0.1955</v>
+        <v>0.2015</v>
       </c>
       <c r="P85" t="n">
         <v>3</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.6475</v>
+        <v>0.6904</v>
       </c>
       <c r="R85" t="n">
         <v>3.643</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>It's just past midnight, when should I run the dishwasher?</t>
+          <t>It's just past midnight. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="L86" t="n">
         <v>0.8100000000000001</v>
@@ -6276,13 +6276,13 @@
         <v>0.85</v>
       </c>
       <c r="O86" t="n">
-        <v>0.8899999999999999</v>
+        <v>0.899</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.0722</v>
+        <v>0.0576</v>
       </c>
       <c r="R86" t="n">
         <v>0.927</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>It's just past midnight, when should I run the dishwasher?</t>
+          <t>It's just past midnight. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6350,7 +6350,7 @@
         <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.0722</v>
+        <v>0.0796</v>
       </c>
       <c r="R87" t="n">
         <v>0.989</v>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>It's just past midnight, when should I run the dishwasher?</t>
+          <t>It's just past midnight. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="L88" t="n">
         <v>0.79</v>
@@ -6412,13 +6412,13 @@
         <v>0.52</v>
       </c>
       <c r="O88" t="n">
-        <v>0.6654999999999999</v>
+        <v>0.6745</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.304</v>
+        <v>0.3111</v>
       </c>
       <c r="R88" t="n">
         <v>0.989</v>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L89" t="n">
         <v>0.97</v>
@@ -6480,13 +6480,13 @@
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0.9685</v>
+        <v>0.9715</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.0703</v>
+        <v>0.075</v>
       </c>
       <c r="R89" t="n">
         <v>0.396</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L90" t="n">
         <v>0.97</v>
@@ -6548,13 +6548,13 @@
         <v>0.52</v>
       </c>
       <c r="O90" t="n">
-        <v>0.8314999999999999</v>
+        <v>0.8345</v>
       </c>
       <c r="P90" t="n">
         <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.0353</v>
+        <v>0.0379</v>
       </c>
       <c r="R90" t="n">
         <v>0.396</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L91" t="n">
         <v>0.98</v>
@@ -6616,13 +6616,13 @@
         <v>0.44</v>
       </c>
       <c r="O91" t="n">
-        <v>0.7889999999999999</v>
+        <v>0.792</v>
       </c>
       <c r="P91" t="n">
         <v>3</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.0353</v>
+        <v>0.0379</v>
       </c>
       <c r="R91" t="n">
         <v>0.371</v>
@@ -6687,10 +6687,10 @@
         <v>0.35</v>
       </c>
       <c r="P92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.7105</v>
+        <v>0.7741</v>
       </c>
       <c r="R92" t="n">
         <v>3.643</v>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="L93" t="n">
         <v>0.07000000000000001</v>
@@ -6752,13 +6752,13 @@
         <v>0.41</v>
       </c>
       <c r="O93" t="n">
-        <v>0.331</v>
+        <v>0.37</v>
       </c>
       <c r="P93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.35</v>
+        <v>0.282</v>
       </c>
       <c r="R93" t="n">
         <v>3.416</v>
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="L94" t="n">
         <v>0.07000000000000001</v>
@@ -6820,13 +6820,13 @@
         <v>0.19</v>
       </c>
       <c r="O94" t="n">
-        <v>0.28</v>
+        <v>0.319</v>
       </c>
       <c r="P94" t="n">
         <v>3</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.35</v>
+        <v>0.282</v>
       </c>
       <c r="R94" t="n">
         <v>3.416</v>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the dryer. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the dryer. When should I run it?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6894,7 +6894,7 @@
         <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.5075</v>
+        <v>0.553</v>
       </c>
       <c r="R95" t="n">
         <v>2.603</v>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the dryer. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the dryer. When should I run it?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="L96" t="n">
         <v>0.36</v>
@@ -6956,13 +6956,13 @@
         <v>0.15</v>
       </c>
       <c r="O96" t="n">
-        <v>0.3795</v>
+        <v>0.4095</v>
       </c>
       <c r="P96" t="n">
         <v>3</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.25</v>
+        <v>0.2014</v>
       </c>
       <c r="R96" t="n">
         <v>2.44</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I'm trying to figure out when to start the dryer. When should I run it?</t>
+          <t>It's mid-afternoon, about 2, and I'm trying to figure out when to start the dryer. When should I run it?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7030,7 +7030,7 @@
         <v>2</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.25</v>
+        <v>0.2722</v>
       </c>
       <c r="R97" t="n">
         <v>2.603</v>
@@ -7098,7 +7098,7 @@
         <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.2334</v>
+        <v>0.2544</v>
       </c>
       <c r="R98" t="n">
         <v>1.197</v>
@@ -7166,7 +7166,7 @@
         <v>2</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.115</v>
+        <v>0.1252</v>
       </c>
       <c r="R99" t="n">
         <v>1.197</v>
@@ -7216,7 +7216,7 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="L100" t="n">
         <v>0.75</v>
@@ -7228,13 +7228,13 @@
         <v>0.36</v>
       </c>
       <c r="O100" t="n">
-        <v>0.7195</v>
+        <v>0.7315</v>
       </c>
       <c r="P100" t="n">
         <v>3</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.115</v>
+        <v>0.0927</v>
       </c>
       <c r="R100" t="n">
         <v>1.122</v>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>It's around 8 at night, when should I run the dishwasher?</t>
+          <t>It's around 8 at night. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7296,13 +7296,13 @@
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.9055000000000001</v>
+        <v>0.9055</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.0722</v>
+        <v>0.0796</v>
       </c>
       <c r="R101" t="n">
         <v>0.989</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>It's around 8 at night, when should I run the dishwasher?</t>
+          <t>It's around 8 at night. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7364,13 +7364,13 @@
         <v>0.67</v>
       </c>
       <c r="O102" t="n">
-        <v>0.8330000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="P102" t="n">
         <v>2</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.0722</v>
+        <v>0.0796</v>
       </c>
       <c r="R102" t="n">
         <v>0.927</v>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>It's around 8 at night, when should I run the dishwasher?</t>
+          <t>It's around 8 at night. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="L103" t="n">
         <v>0.8100000000000001</v>
@@ -7432,13 +7432,13 @@
         <v>0.36</v>
       </c>
       <c r="O103" t="n">
-        <v>0.7585000000000001</v>
+        <v>0.7675</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.0722</v>
+        <v>0.0576</v>
       </c>
       <c r="R103" t="n">
         <v>0.927</v>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="L104" t="n">
         <v>0.6</v>
@@ -7500,7 +7500,7 @@
         <v>0.35</v>
       </c>
       <c r="O104" t="n">
-        <v>0.5835</v>
+        <v>0.5895</v>
       </c>
       <c r="P104" t="n">
         <v>3</v>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="L105" t="n">
         <v>0.6</v>
@@ -7568,7 +7568,7 @@
         <v>0.36</v>
       </c>
       <c r="O105" t="n">
-        <v>0.609</v>
+        <v>0.615</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="L106" t="n">
         <v>0.63</v>
@@ -7636,7 +7636,7 @@
         <v>0.35</v>
       </c>
       <c r="O106" t="n">
-        <v>0.632</v>
+        <v>0.638</v>
       </c>
       <c r="P106" t="n">
         <v>1</v>
@@ -7704,13 +7704,13 @@
         <v>0.93</v>
       </c>
       <c r="O107" t="n">
-        <v>0.9814999999999998</v>
+        <v>0.9815</v>
       </c>
       <c r="P107" t="n">
         <v>1</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.0205</v>
+        <v>0.0219</v>
       </c>
       <c r="R107" t="n">
         <v>0.229</v>
@@ -7778,7 +7778,7 @@
         <v>2</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.0205</v>
+        <v>0.0219</v>
       </c>
       <c r="R108" t="n">
         <v>0.229</v>
@@ -7846,7 +7846,7 @@
         <v>3</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.0205</v>
+        <v>0.0219</v>
       </c>
       <c r="R109" t="n">
         <v>0.229</v>
@@ -7911,10 +7911,10 @@
         <v>0.4165</v>
       </c>
       <c r="P110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.928</v>
+        <v>0.9497</v>
       </c>
       <c r="R110" t="n">
         <v>3.019</v>
@@ -7982,7 +7982,7 @@
         <v>3</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.928</v>
+        <v>0.9497</v>
       </c>
       <c r="R111" t="n">
         <v>3.019</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="L112" t="n">
         <v>0.24</v>
@@ -8044,13 +8044,13 @@
         <v>0.25</v>
       </c>
       <c r="O112" t="n">
-        <v>0.4105</v>
+        <v>0.4375</v>
       </c>
       <c r="P112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.2204</v>
+        <v>0.1758</v>
       </c>
       <c r="R112" t="n">
         <v>2.83</v>
@@ -8112,13 +8112,13 @@
         <v>0.92</v>
       </c>
       <c r="O113" t="n">
-        <v>0.9514999999999999</v>
+        <v>0.9515</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.045</v>
+        <v>0.049</v>
       </c>
       <c r="R113" t="n">
         <v>0.468</v>
@@ -8180,13 +8180,13 @@
         <v>0.83</v>
       </c>
       <c r="O114" t="n">
-        <v>0.9259999999999999</v>
+        <v>0.926</v>
       </c>
       <c r="P114" t="n">
         <v>2</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.045</v>
+        <v>0.049</v>
       </c>
       <c r="R114" t="n">
         <v>0.468</v>
@@ -8254,7 +8254,7 @@
         <v>3</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.0914</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="R115" t="n">
         <v>0.468</v>
@@ -8316,13 +8316,13 @@
         <v>0.91</v>
       </c>
       <c r="O116" t="n">
-        <v>0.9610000000000001</v>
+        <v>0.961</v>
       </c>
       <c r="P116" t="n">
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.0289</v>
+        <v>0.0319</v>
       </c>
       <c r="R116" t="n">
         <v>0.396</v>
@@ -8390,7 +8390,7 @@
         <v>2</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.0289</v>
+        <v>0.0319</v>
       </c>
       <c r="R117" t="n">
         <v>0.396</v>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="L118" t="n">
         <v>0.97</v>
@@ -8452,13 +8452,13 @@
         <v>0.43</v>
       </c>
       <c r="O118" t="n">
-        <v>0.7779999999999999</v>
+        <v>0.781</v>
       </c>
       <c r="P118" t="n">
         <v>3</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.1216</v>
+        <v>0.1244</v>
       </c>
       <c r="R118" t="n">
         <v>0.396</v>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8526,7 +8526,7 @@
         <v>1</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.2604</v>
+        <v>0.279</v>
       </c>
       <c r="R119" t="n">
         <v>2.915</v>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8588,13 +8588,13 @@
         <v>0.82</v>
       </c>
       <c r="O120" t="n">
-        <v>0.5760000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="P120" t="n">
         <v>2</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.2604</v>
+        <v>0.279</v>
       </c>
       <c r="R120" t="n">
         <v>2.915</v>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8644,7 +8644,7 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="L121" t="n">
         <v>0.22</v>
@@ -8656,13 +8656,13 @@
         <v>0.54</v>
       </c>
       <c r="O121" t="n">
-        <v>0.3760000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="P121" t="n">
         <v>3</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.518</v>
+        <v>0.5523</v>
       </c>
       <c r="R121" t="n">
         <v>2.915</v>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -8724,13 +8724,13 @@
         <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>0.518</v>
+        <v>0.521</v>
       </c>
       <c r="P122" t="n">
         <v>1</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.3255</v>
+        <v>0.3487</v>
       </c>
       <c r="R122" t="n">
         <v>3.643</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8780,7 +8780,7 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.67</v>
       </c>
       <c r="O123" t="n">
-        <v>0.4245000000000001</v>
+        <v>0.4275</v>
       </c>
       <c r="P123" t="n">
         <v>2</v>
       </c>
       <c r="Q123" t="n">
-        <v>0.3255</v>
+        <v>0.3487</v>
       </c>
       <c r="R123" t="n">
         <v>3.643</v>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8848,7 +8848,7 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -8860,13 +8860,13 @@
         <v>0.43</v>
       </c>
       <c r="O124" t="n">
-        <v>0.2095</v>
+        <v>0.2155</v>
       </c>
       <c r="P124" t="n">
         <v>3</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.6475</v>
+        <v>0.6904</v>
       </c>
       <c r="R124" t="n">
         <v>3.643</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -8928,13 +8928,13 @@
         <v>1</v>
       </c>
       <c r="O125" t="n">
-        <v>0.554</v>
+        <v>0.494</v>
       </c>
       <c r="P125" t="n">
         <v>1</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.245</v>
+        <v>0.4195</v>
       </c>
       <c r="R125" t="n">
         <v>3.643</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -8996,13 +8996,13 @@
         <v>0.78</v>
       </c>
       <c r="O126" t="n">
-        <v>0.493</v>
+        <v>0.433</v>
       </c>
       <c r="P126" t="n">
         <v>2</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.245</v>
+        <v>0.4195</v>
       </c>
       <c r="R126" t="n">
         <v>3.643</v>
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>0.22</v>
+        <v>0.48</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -9064,13 +9064,13 @@
         <v>0.62</v>
       </c>
       <c r="O127" t="n">
-        <v>0.307</v>
+        <v>0.385</v>
       </c>
       <c r="P127" t="n">
         <v>3</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4195</v>
       </c>
       <c r="R127" t="n">
         <v>3.643</v>
@@ -9132,13 +9132,13 @@
         <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>0.8650000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="P128" t="n">
         <v>1</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.095</v>
+        <v>0.1048</v>
       </c>
       <c r="R128" t="n">
         <v>1.301</v>
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="L129" t="n">
         <v>0.7</v>
@@ -9200,13 +9200,13 @@
         <v>0.64</v>
       </c>
       <c r="O129" t="n">
-        <v>0.628</v>
+        <v>0.64</v>
       </c>
       <c r="P129" t="n">
         <v>3</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.4</v>
+        <v>0.4093</v>
       </c>
       <c r="R129" t="n">
         <v>1.301</v>
@@ -9274,7 +9274,7 @@
         <v>2</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.095</v>
+        <v>0.1048</v>
       </c>
       <c r="R130" t="n">
         <v>1.22</v>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L131" t="n">
         <v>0.98</v>
@@ -9336,13 +9336,13 @@
         <v>1</v>
       </c>
       <c r="O131" t="n">
-        <v>0.993</v>
+        <v>0.987</v>
       </c>
       <c r="P131" t="n">
         <v>1</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.0245</v>
+        <v>0.042</v>
       </c>
       <c r="R131" t="n">
         <v>0.364</v>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L132" t="n">
         <v>0.98</v>
@@ -9404,13 +9404,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="O132" t="n">
-        <v>0.8499999999999999</v>
+        <v>0.859</v>
       </c>
       <c r="P132" t="n">
         <v>2</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.056</v>
+        <v>0.042</v>
       </c>
       <c r="R132" t="n">
         <v>0.364</v>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L133" t="n">
         <v>0.98</v>
@@ -9472,13 +9472,13 @@
         <v>0.15</v>
       </c>
       <c r="O133" t="n">
-        <v>0.7415</v>
+        <v>0.7355</v>
       </c>
       <c r="P133" t="n">
         <v>3</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.0245</v>
+        <v>0.042</v>
       </c>
       <c r="R133" t="n">
         <v>0.342</v>
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="L134" t="n">
         <v>0.31</v>
@@ -9540,13 +9540,13 @@
         <v>1</v>
       </c>
       <c r="O134" t="n">
-        <v>0.6925</v>
+        <v>0.6505</v>
       </c>
       <c r="P134" t="n">
         <v>1</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.175</v>
+        <v>0.2997</v>
       </c>
       <c r="R134" t="n">
         <v>2.603</v>
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>0.78</v>
+        <v>0.57</v>
       </c>
       <c r="L135" t="n">
         <v>0.31</v>
@@ -9608,13 +9608,13 @@
         <v>0.34</v>
       </c>
       <c r="O135" t="n">
-        <v>0.4955</v>
+        <v>0.4325</v>
       </c>
       <c r="P135" t="n">
         <v>2</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.175</v>
+        <v>0.3497</v>
       </c>
       <c r="R135" t="n">
         <v>2.603</v>
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="L136" t="n">
         <v>0.36</v>
@@ -9676,13 +9676,13 @@
         <v>0.18</v>
       </c>
       <c r="O136" t="n">
-        <v>0.473</v>
+        <v>0.431</v>
       </c>
       <c r="P136" t="n">
         <v>3</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.175</v>
+        <v>0.2997</v>
       </c>
       <c r="R136" t="n">
         <v>2.44</v>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's late morning, around 11, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9750,7 +9750,7 @@
         <v>1</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0922</v>
       </c>
       <c r="R137" t="n">
         <v>1.145</v>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's late morning, around 11, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="L138" t="n">
         <v>0.74</v>
@@ -9812,13 +9812,13 @@
         <v>0.67</v>
       </c>
       <c r="O138" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6805</v>
       </c>
       <c r="P138" t="n">
         <v>3</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.352</v>
+        <v>0.3602</v>
       </c>
       <c r="R138" t="n">
         <v>1.145</v>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>It's late morning, around 11 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's late morning, around 11, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9886,7 +9886,7 @@
         <v>2</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0922</v>
       </c>
       <c r="R139" t="n">
         <v>1.145</v>
@@ -9936,7 +9936,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L140" t="n">
         <v>0.95</v>
@@ -9948,13 +9948,13 @@
         <v>1</v>
       </c>
       <c r="O140" t="n">
-        <v>0.9794999999999999</v>
+        <v>0.9735</v>
       </c>
       <c r="P140" t="n">
         <v>1</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.0315</v>
+        <v>0.049</v>
       </c>
       <c r="R140" t="n">
         <v>0.468</v>
@@ -10004,7 +10004,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L141" t="n">
         <v>0.95</v>
@@ -10016,13 +10016,13 @@
         <v>0.3</v>
       </c>
       <c r="O141" t="n">
-        <v>0.7685</v>
+        <v>0.7415</v>
       </c>
       <c r="P141" t="n">
         <v>2</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.0315</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="R141" t="n">
         <v>0.468</v>
@@ -10090,7 +10090,7 @@
         <v>3</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.0315</v>
+        <v>0.0363</v>
       </c>
       <c r="R142" t="n">
         <v>0.439</v>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -10140,7 +10140,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L143" t="n">
         <v>0.7</v>
@@ -10152,7 +10152,7 @@
         <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>0.832</v>
+        <v>0.838</v>
       </c>
       <c r="P143" t="n">
         <v>1</v>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -10208,7 +10208,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L144" t="n">
         <v>0.7</v>
@@ -10220,7 +10220,7 @@
         <v>0.67</v>
       </c>
       <c r="O144" t="n">
-        <v>0.7385</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="P144" t="n">
         <v>2</v>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>It's mid-morning, about 10 and I need to run the dishwasher. When should I start it?</t>
+          <t>It's mid-morning, about 10, and I need to run the dishwasher. When should I start it?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L145" t="n">
         <v>0.72</v>
@@ -10288,7 +10288,7 @@
         <v>0.27</v>
       </c>
       <c r="O145" t="n">
-        <v>0.6395</v>
+        <v>0.6455</v>
       </c>
       <c r="P145" t="n">
         <v>3</v>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, just past 3, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10344,7 +10344,7 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="L146" t="n">
         <v>0.97</v>
@@ -10356,7 +10356,7 @@
         <v>1</v>
       </c>
       <c r="O146" t="n">
-        <v>0.9774999999999999</v>
+        <v>0.9805</v>
       </c>
       <c r="P146" t="n">
         <v>1</v>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, just past 3, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="L147" t="n">
         <v>0.97</v>
@@ -10424,7 +10424,7 @@
         <v>0.68</v>
       </c>
       <c r="O147" t="n">
-        <v>0.8875</v>
+        <v>0.8905</v>
       </c>
       <c r="P147" t="n">
         <v>2</v>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, just past 3, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="L148" t="n">
         <v>0.98</v>
@@ -10492,7 +10492,7 @@
         <v>0.15</v>
       </c>
       <c r="O148" t="n">
-        <v>0.7295</v>
+        <v>0.7325</v>
       </c>
       <c r="P148" t="n">
         <v>3</v>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="K149" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="L149" t="n">
         <v>0.22</v>
@@ -10560,7 +10560,7 @@
         <v>1</v>
       </c>
       <c r="O149" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="P149" t="n">
         <v>1</v>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10616,7 +10616,7 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="L150" t="n">
         <v>0.22</v>
@@ -10628,7 +10628,7 @@
         <v>0.6</v>
       </c>
       <c r="O150" t="n">
-        <v>0.454</v>
+        <v>0.469</v>
       </c>
       <c r="P150" t="n">
         <v>2</v>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>It's just past 9 AM, when should I run the dryer?</t>
+          <t>It's just past 9 AM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="L151" t="n">
         <v>0.27</v>
@@ -10696,7 +10696,7 @@
         <v>0.21</v>
       </c>
       <c r="O151" t="n">
-        <v>0.3129999999999999</v>
+        <v>0.328</v>
       </c>
       <c r="P151" t="n">
         <v>3</v>
@@ -10752,7 +10752,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="L152" t="n">
         <v>0.79</v>
@@ -10764,7 +10764,7 @@
         <v>1</v>
       </c>
       <c r="O152" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8845</v>
       </c>
       <c r="P152" t="n">
         <v>1</v>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="K153" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="L153" t="n">
         <v>0.79</v>
@@ -10832,7 +10832,7 @@
         <v>0.67</v>
       </c>
       <c r="O153" t="n">
-        <v>0.802</v>
+        <v>0.805</v>
       </c>
       <c r="P153" t="n">
         <v>2</v>
@@ -10888,7 +10888,7 @@
         </is>
       </c>
       <c r="K154" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="L154" t="n">
         <v>0.8100000000000001</v>
@@ -10900,7 +10900,7 @@
         <v>0.43</v>
       </c>
       <c r="O154" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="P154" t="n">
         <v>3</v>
@@ -10956,7 +10956,7 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
@@ -10968,7 +10968,7 @@
         <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>0.9939999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="P155" t="n">
         <v>1</v>
@@ -11024,7 +11024,7 @@
         </is>
       </c>
       <c r="K156" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L156" t="n">
         <v>1</v>
@@ -11036,7 +11036,7 @@
         <v>0.57</v>
       </c>
       <c r="O156" t="n">
-        <v>0.8694999999999999</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="P156" t="n">
         <v>2</v>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L157" t="n">
         <v>1</v>
@@ -11104,7 +11104,7 @@
         <v>0.41</v>
       </c>
       <c r="O157" t="n">
-        <v>0.7914999999999999</v>
+        <v>0.7945</v>
       </c>
       <c r="P157" t="n">
         <v>3</v>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -11178,7 +11178,7 @@
         <v>1</v>
       </c>
       <c r="Q158" t="n">
-        <v>0.032</v>
+        <v>0.0365</v>
       </c>
       <c r="R158" t="n">
         <v>0.208</v>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -11246,7 +11246,7 @@
         <v>2</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.014</v>
+        <v>0.0187</v>
       </c>
       <c r="R159" t="n">
         <v>0.208</v>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>It's late afternoon, around 4 and I need to run the washing machine. When should I start it?</t>
+          <t>It's late afternoon, around 4, and I need to run the washing machine. When should I start it?</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -11308,13 +11308,13 @@
         <v>0.29</v>
       </c>
       <c r="O160" t="n">
-        <v>0.7654999999999998</v>
+        <v>0.7655</v>
       </c>
       <c r="P160" t="n">
         <v>3</v>
       </c>
       <c r="Q160" t="n">
-        <v>0.014</v>
+        <v>0.0138</v>
       </c>
       <c r="R160" t="n">
         <v>0.195</v>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening, when should I run the washing machine?</t>
+          <t>It's around 5 in the evening. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -11364,7 +11364,7 @@
         </is>
       </c>
       <c r="K161" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
@@ -11376,13 +11376,13 @@
         <v>1</v>
       </c>
       <c r="O161" t="n">
-        <v>0.9939999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="P161" t="n">
         <v>1</v>
       </c>
       <c r="Q161" t="n">
-        <v>0.0368</v>
+        <v>0.0322</v>
       </c>
       <c r="R161" t="n">
         <v>0.239</v>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening, when should I run the washing machine?</t>
+          <t>It's around 5 in the evening. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -11444,13 +11444,13 @@
         <v>0.43</v>
       </c>
       <c r="O162" t="n">
-        <v>0.8324999999999999</v>
+        <v>0.8325</v>
       </c>
       <c r="P162" t="n">
         <v>3</v>
       </c>
       <c r="Q162" t="n">
-        <v>0.0161</v>
+        <v>0.0276</v>
       </c>
       <c r="R162" t="n">
         <v>0.239</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>It's around 5 in the evening, when should I run the washing machine?</t>
+          <t>It's around 5 in the evening. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -11512,13 +11512,13 @@
         <v>0.52</v>
       </c>
       <c r="O163" t="n">
-        <v>0.8479999999999999</v>
+        <v>0.848</v>
       </c>
       <c r="P163" t="n">
         <v>2</v>
       </c>
       <c r="Q163" t="n">
-        <v>0.0161</v>
+        <v>0.0276</v>
       </c>
       <c r="R163" t="n">
         <v>0.239</v>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, just past 3, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -11586,7 +11586,7 @@
         <v>3</v>
       </c>
       <c r="Q164" t="n">
-        <v>1.024</v>
+        <v>1.0479</v>
       </c>
       <c r="R164" t="n">
         <v>3.331</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, just past 3, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -11648,13 +11648,13 @@
         <v>0.49</v>
       </c>
       <c r="O165" t="n">
-        <v>0.4350000000000001</v>
+        <v>0.435</v>
       </c>
       <c r="P165" t="n">
         <v>1</v>
       </c>
       <c r="Q165" t="n">
-        <v>0.2432</v>
+        <v>0.2682</v>
       </c>
       <c r="R165" t="n">
         <v>3.331</v>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3 and I need to run the dryer. When should I start it?</t>
+          <t>It's late afternoon, just past 3, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11722,7 +11722,7 @@
         <v>2</v>
       </c>
       <c r="Q166" t="n">
-        <v>0.2432</v>
+        <v>0.2682</v>
       </c>
       <c r="R166" t="n">
         <v>3.123</v>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>It's just past 7 PM, when should I run the dryer?</t>
+          <t>It's just past 7 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="K167" t="n">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -11784,13 +11784,13 @@
         <v>1</v>
       </c>
       <c r="O167" t="n">
-        <v>0.554</v>
+        <v>0.464</v>
       </c>
       <c r="P167" t="n">
         <v>1</v>
       </c>
       <c r="Q167" t="n">
-        <v>0.245</v>
+        <v>0.4895</v>
       </c>
       <c r="R167" t="n">
         <v>3.643</v>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>It's just past 7 PM, when should I run the dryer?</t>
+          <t>It's just past 7 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -11840,7 +11840,7 @@
         </is>
       </c>
       <c r="K168" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -11852,13 +11852,13 @@
         <v>0.34</v>
       </c>
       <c r="O168" t="n">
-        <v>0.357</v>
+        <v>0.297</v>
       </c>
       <c r="P168" t="n">
         <v>3</v>
       </c>
       <c r="Q168" t="n">
-        <v>0.245</v>
+        <v>0.4195</v>
       </c>
       <c r="R168" t="n">
         <v>3.643</v>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>It's just past 7 PM, when should I run the dryer?</t>
+          <t>It's just past 7 PM. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -11908,7 +11908,7 @@
         </is>
       </c>
       <c r="K169" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="L169" t="n">
         <v>0.07000000000000001</v>
@@ -11920,13 +11920,13 @@
         <v>0.39</v>
       </c>
       <c r="O169" t="n">
-        <v>0.389</v>
+        <v>0.329</v>
       </c>
       <c r="P169" t="n">
         <v>2</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.245</v>
+        <v>0.4195</v>
       </c>
       <c r="R169" t="n">
         <v>3.416</v>
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="K170" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="L170" t="n">
         <v>0.86</v>
@@ -11988,13 +11988,13 @@
         <v>1</v>
       </c>
       <c r="O170" t="n">
-        <v>0.8610000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="P170" t="n">
         <v>1</v>
       </c>
       <c r="Q170" t="n">
-        <v>0.2304</v>
+        <v>0.2358</v>
       </c>
       <c r="R170" t="n">
         <v>0.75</v>
@@ -12062,7 +12062,7 @@
         <v>2</v>
       </c>
       <c r="Q171" t="n">
-        <v>0.0547</v>
+        <v>0.0604</v>
       </c>
       <c r="R171" t="n">
         <v>0.75</v>
@@ -12130,7 +12130,7 @@
         <v>3</v>
       </c>
       <c r="Q172" t="n">
-        <v>0.0547</v>
+        <v>0.0604</v>
       </c>
       <c r="R172" t="n">
         <v>0.75</v>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="K173" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L173" t="n">
         <v>0.98</v>
@@ -12192,13 +12192,13 @@
         <v>0.93</v>
       </c>
       <c r="O173" t="n">
-        <v>0.9385000000000001</v>
+        <v>0.9325</v>
       </c>
       <c r="P173" t="n">
         <v>1</v>
       </c>
       <c r="Q173" t="n">
-        <v>0.0266</v>
+        <v>0.0456</v>
       </c>
       <c r="R173" t="n">
         <v>0.371</v>
@@ -12248,7 +12248,7 @@
         </is>
       </c>
       <c r="K174" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L174" t="n">
         <v>0.97</v>
@@ -12260,13 +12260,13 @@
         <v>0.39</v>
       </c>
       <c r="O174" t="n">
-        <v>0.8079999999999999</v>
+        <v>0.802</v>
       </c>
       <c r="P174" t="n">
         <v>2</v>
       </c>
       <c r="Q174" t="n">
-        <v>0.0266</v>
+        <v>0.0456</v>
       </c>
       <c r="R174" t="n">
         <v>0.396</v>
@@ -12316,7 +12316,7 @@
         </is>
       </c>
       <c r="K175" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L175" t="n">
         <v>0.97</v>
@@ -12328,13 +12328,13 @@
         <v>0.39</v>
       </c>
       <c r="O175" t="n">
-        <v>0.7929999999999999</v>
+        <v>0.802</v>
       </c>
       <c r="P175" t="n">
         <v>3</v>
       </c>
       <c r="Q175" t="n">
-        <v>0.0608</v>
+        <v>0.0456</v>
       </c>
       <c r="R175" t="n">
         <v>0.396</v>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -12402,7 +12402,7 @@
         <v>1</v>
       </c>
       <c r="Q176" t="n">
-        <v>0.19</v>
+        <v>0.2096</v>
       </c>
       <c r="R176" t="n">
         <v>2.603</v>
@@ -12414,7 +12414,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -12470,7 +12470,7 @@
         <v>2</v>
       </c>
       <c r="Q177" t="n">
-        <v>0.19</v>
+        <v>0.2096</v>
       </c>
       <c r="R177" t="n">
         <v>2.603</v>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>It's late, just past 10 PM and I need to run the dryer. When should I start it?</t>
+          <t>It's late, just past 10 PM, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -12538,7 +12538,7 @@
         <v>3</v>
       </c>
       <c r="Q178" t="n">
-        <v>0.8</v>
+        <v>0.8187</v>
       </c>
       <c r="R178" t="n">
         <v>2.603</v>
@@ -12588,7 +12588,7 @@
         </is>
       </c>
       <c r="K179" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L179" t="n">
         <v>0.98</v>
@@ -12600,13 +12600,13 @@
         <v>0.85</v>
       </c>
       <c r="O179" t="n">
-        <v>0.9235</v>
+        <v>0.9265</v>
       </c>
       <c r="P179" t="n">
         <v>1</v>
       </c>
       <c r="Q179" t="n">
-        <v>0.035</v>
+        <v>0.0282</v>
       </c>
       <c r="R179" t="n">
         <v>0.342</v>
@@ -12668,13 +12668,13 @@
         <v>0.44</v>
       </c>
       <c r="O180" t="n">
-        <v>0.8239999999999998</v>
+        <v>0.824</v>
       </c>
       <c r="P180" t="n">
         <v>2</v>
       </c>
       <c r="Q180" t="n">
-        <v>0.035</v>
+        <v>0.0381</v>
       </c>
       <c r="R180" t="n">
         <v>0.364</v>
@@ -12742,7 +12742,7 @@
         <v>3</v>
       </c>
       <c r="Q181" t="n">
-        <v>0.0711</v>
+        <v>0.0774</v>
       </c>
       <c r="R181" t="n">
         <v>0.364</v>
@@ -12792,7 +12792,7 @@
         </is>
       </c>
       <c r="K182" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="L182" t="n">
         <v>0.21</v>
@@ -12804,13 +12804,13 @@
         <v>0.85</v>
       </c>
       <c r="O182" t="n">
-        <v>0.546</v>
+        <v>0.576</v>
       </c>
       <c r="P182" t="n">
         <v>1</v>
       </c>
       <c r="Q182" t="n">
-        <v>0.279</v>
+        <v>0.2294</v>
       </c>
       <c r="R182" t="n">
         <v>2.928</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="K183" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="L183" t="n">
         <v>0.15</v>
@@ -12872,13 +12872,13 @@
         <v>0.52</v>
       </c>
       <c r="O183" t="n">
-        <v>0.4535</v>
+        <v>0.4565</v>
       </c>
       <c r="P183" t="n">
         <v>2</v>
       </c>
       <c r="Q183" t="n">
-        <v>0.279</v>
+        <v>0.2989</v>
       </c>
       <c r="R183" t="n">
         <v>3.123</v>
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="K184" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="L184" t="n">
         <v>0.15</v>
@@ -12940,13 +12940,13 @@
         <v>0.39</v>
       </c>
       <c r="O184" t="n">
-        <v>0.29</v>
+        <v>0.293</v>
       </c>
       <c r="P184" t="n">
         <v>3</v>
       </c>
       <c r="Q184" t="n">
-        <v>0.555</v>
+        <v>0.5918</v>
       </c>
       <c r="R184" t="n">
         <v>3.123</v>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -12996,7 +12996,7 @@
         </is>
       </c>
       <c r="K185" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="L185" t="n">
         <v>0.95</v>
@@ -13008,13 +13008,13 @@
         <v>0.93</v>
       </c>
       <c r="O185" t="n">
-        <v>0.9319999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="P185" t="n">
         <v>1</v>
       </c>
       <c r="Q185" t="n">
-        <v>0.0396</v>
+        <v>0.031</v>
       </c>
       <c r="R185" t="n">
         <v>0.439</v>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -13076,13 +13076,13 @@
         <v>0.39</v>
       </c>
       <c r="O186" t="n">
-        <v>0.7949999999999999</v>
+        <v>0.795</v>
       </c>
       <c r="P186" t="n">
         <v>2</v>
       </c>
       <c r="Q186" t="n">
-        <v>0.0396</v>
+        <v>0.0421</v>
       </c>
       <c r="R186" t="n">
         <v>0.468</v>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>It's getting close to midnight, when should I run the washing machine?</t>
+          <t>It's getting close to midnight. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -13132,7 +13132,7 @@
         </is>
       </c>
       <c r="K187" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="L187" t="n">
         <v>0.95</v>
@@ -13144,13 +13144,13 @@
         <v>0.43</v>
       </c>
       <c r="O187" t="n">
-        <v>0.791</v>
+        <v>0.794</v>
       </c>
       <c r="P187" t="n">
         <v>3</v>
       </c>
       <c r="Q187" t="n">
-        <v>0.0774</v>
+        <v>0.082</v>
       </c>
       <c r="R187" t="n">
         <v>0.468</v>
@@ -13212,13 +13212,13 @@
         <v>1</v>
       </c>
       <c r="O188" t="n">
-        <v>0.8650000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="P188" t="n">
         <v>1</v>
       </c>
       <c r="Q188" t="n">
-        <v>0.095</v>
+        <v>0.1048</v>
       </c>
       <c r="R188" t="n">
         <v>1.301</v>
@@ -13280,13 +13280,13 @@
         <v>0.67</v>
       </c>
       <c r="O189" t="n">
-        <v>0.7715000000000001</v>
+        <v>0.7715</v>
       </c>
       <c r="P189" t="n">
         <v>2</v>
       </c>
       <c r="Q189" t="n">
-        <v>0.095</v>
+        <v>0.1048</v>
       </c>
       <c r="R189" t="n">
         <v>1.301</v>
@@ -13354,7 +13354,7 @@
         <v>3</v>
       </c>
       <c r="Q190" t="n">
-        <v>0.095</v>
+        <v>0.1048</v>
       </c>
       <c r="R190" t="n">
         <v>1.301</v>
@@ -13366,7 +13366,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -13404,7 +13404,7 @@
         </is>
       </c>
       <c r="K191" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="L191" t="n">
         <v>0.31</v>
@@ -13416,13 +13416,13 @@
         <v>1</v>
       </c>
       <c r="O191" t="n">
-        <v>0.5935</v>
+        <v>0.6505</v>
       </c>
       <c r="P191" t="n">
         <v>1</v>
       </c>
       <c r="Q191" t="n">
-        <v>0.4</v>
+        <v>0.2997</v>
       </c>
       <c r="R191" t="n">
         <v>2.603</v>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -13472,7 +13472,7 @@
         </is>
       </c>
       <c r="K192" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="L192" t="n">
         <v>0.31</v>
@@ -13484,13 +13484,13 @@
         <v>0.8</v>
       </c>
       <c r="O192" t="n">
-        <v>0.5375</v>
+        <v>0.5735</v>
       </c>
       <c r="P192" t="n">
         <v>2</v>
       </c>
       <c r="Q192" t="n">
-        <v>0.4</v>
+        <v>0.3497</v>
       </c>
       <c r="R192" t="n">
         <v>2.603</v>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>It's mid-afternoon, about 2 and I need to run the dryer. When should I start it?</t>
+          <t>It's mid-afternoon, about 2, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="K193" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="L193" t="n">
         <v>0.31</v>
@@ -13552,13 +13552,13 @@
         <v>0.46</v>
       </c>
       <c r="O193" t="n">
-        <v>0.5335</v>
+        <v>0.4915</v>
       </c>
       <c r="P193" t="n">
         <v>3</v>
       </c>
       <c r="Q193" t="n">
-        <v>0.175</v>
+        <v>0.2997</v>
       </c>
       <c r="R193" t="n">
         <v>2.603</v>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>It's just after 8 AM, when should I run the dishwasher?</t>
+          <t>It's just after 9 AM. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="K194" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="L194" t="n">
         <v>0.74</v>
@@ -13620,13 +13620,13 @@
         <v>1</v>
       </c>
       <c r="O194" t="n">
-        <v>0.8850000000000001</v>
+        <v>0.873</v>
       </c>
       <c r="P194" t="n">
         <v>1</v>
       </c>
       <c r="Q194" t="n">
-        <v>0.077</v>
+        <v>0.1198</v>
       </c>
       <c r="R194" t="n">
         <v>1.145</v>
@@ -13638,7 +13638,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>It's just after 8 AM, when should I run the dishwasher?</t>
+          <t>It's just after 9 AM. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -13676,7 +13676,7 @@
         </is>
       </c>
       <c r="K195" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="L195" t="n">
         <v>0.74</v>
@@ -13688,13 +13688,13 @@
         <v>0.58</v>
       </c>
       <c r="O195" t="n">
-        <v>0.722</v>
+        <v>0.701</v>
       </c>
       <c r="P195" t="n">
         <v>2</v>
       </c>
       <c r="Q195" t="n">
-        <v>0.176</v>
+        <v>0.2433</v>
       </c>
       <c r="R195" t="n">
         <v>1.145</v>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>It's just after 8 AM, when should I run the dishwasher?</t>
+          <t>It's just after 9 AM. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -13744,7 +13744,7 @@
         </is>
       </c>
       <c r="K196" t="n">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="L196" t="n">
         <v>0.74</v>
@@ -13756,13 +13756,13 @@
         <v>0.3</v>
       </c>
       <c r="O196" t="n">
-        <v>0.676</v>
+        <v>0.613</v>
       </c>
       <c r="P196" t="n">
         <v>3</v>
       </c>
       <c r="Q196" t="n">
-        <v>0.077</v>
+        <v>0.2433</v>
       </c>
       <c r="R196" t="n">
         <v>1.145</v>
@@ -13812,7 +13812,7 @@
         </is>
       </c>
       <c r="K197" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L197" t="n">
         <v>0.98</v>
@@ -13824,13 +13824,13 @@
         <v>0.85</v>
       </c>
       <c r="O197" t="n">
-        <v>0.9265000000000001</v>
+        <v>0.9205</v>
       </c>
       <c r="P197" t="n">
         <v>1</v>
       </c>
       <c r="Q197" t="n">
-        <v>0.0266</v>
+        <v>0.0456</v>
       </c>
       <c r="R197" t="n">
         <v>0.371</v>
@@ -13880,7 +13880,7 @@
         </is>
       </c>
       <c r="K198" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="L198" t="n">
         <v>0.97</v>
@@ -13892,13 +13892,13 @@
         <v>0.35</v>
       </c>
       <c r="O198" t="n">
-        <v>0.7959999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="P198" t="n">
         <v>2</v>
       </c>
       <c r="Q198" t="n">
-        <v>0.0266</v>
+        <v>0.0456</v>
       </c>
       <c r="R198" t="n">
         <v>0.396</v>
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="K199" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L199" t="n">
         <v>0.97</v>
@@ -13960,13 +13960,13 @@
         <v>0.2</v>
       </c>
       <c r="O199" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.7415</v>
       </c>
       <c r="P199" t="n">
         <v>3</v>
       </c>
       <c r="Q199" t="n">
-        <v>0.0608</v>
+        <v>0.0456</v>
       </c>
       <c r="R199" t="n">
         <v>0.396</v>
@@ -14016,7 +14016,7 @@
         </is>
       </c>
       <c r="K200" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L200" t="n">
         <v>0.27</v>
@@ -14028,13 +14028,13 @@
         <v>0.85</v>
       </c>
       <c r="O200" t="n">
-        <v>0.597</v>
+        <v>0.621</v>
       </c>
       <c r="P200" t="n">
         <v>1</v>
       </c>
       <c r="Q200" t="n">
-        <v>0.2128</v>
+        <v>0.1697</v>
       </c>
       <c r="R200" t="n">
         <v>2.733</v>
@@ -14084,7 +14084,7 @@
         </is>
       </c>
       <c r="K201" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="L201" t="n">
         <v>0.22</v>
@@ -14096,13 +14096,13 @@
         <v>0.41</v>
       </c>
       <c r="O201" t="n">
-        <v>0.4695</v>
+        <v>0.4665</v>
       </c>
       <c r="P201" t="n">
         <v>2</v>
       </c>
       <c r="Q201" t="n">
-        <v>0.2128</v>
+        <v>0.2347</v>
       </c>
       <c r="R201" t="n">
         <v>2.915</v>
@@ -14170,7 +14170,7 @@
         <v>3</v>
       </c>
       <c r="Q202" t="n">
-        <v>0.896</v>
+        <v>0.9169</v>
       </c>
       <c r="R202" t="n">
         <v>2.915</v>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
+          <t>It's late morning, just before noon, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -14232,13 +14232,13 @@
         <v>1</v>
       </c>
       <c r="O203" t="n">
-        <v>0.6595000000000001</v>
+        <v>0.6595</v>
       </c>
       <c r="P203" t="n">
         <v>1</v>
       </c>
       <c r="Q203" t="n">
-        <v>0.25</v>
+        <v>0.2722</v>
       </c>
       <c r="R203" t="n">
         <v>2.603</v>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
+          <t>It's late morning, just before noon, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -14300,13 +14300,13 @@
         <v>0.67</v>
       </c>
       <c r="O204" t="n">
-        <v>0.4550000000000001</v>
+        <v>0.455</v>
       </c>
       <c r="P204" t="n">
         <v>2</v>
       </c>
       <c r="Q204" t="n">
-        <v>0.5075</v>
+        <v>0.553</v>
       </c>
       <c r="R204" t="n">
         <v>2.603</v>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>It's late morning, just before noon and I need to run the dryer. When should I start it?</t>
+          <t>It's late morning, just before noon, and I need to run the dryer. When should I start it?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -14356,7 +14356,7 @@
         </is>
       </c>
       <c r="K205" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="L205" t="n">
         <v>0.36</v>
@@ -14368,13 +14368,13 @@
         <v>0.15</v>
       </c>
       <c r="O205" t="n">
-        <v>0.4075</v>
+        <v>0.4375</v>
       </c>
       <c r="P205" t="n">
         <v>3</v>
       </c>
       <c r="Q205" t="n">
-        <v>0.25</v>
+        <v>0.2014</v>
       </c>
       <c r="R205" t="n">
         <v>2.44</v>
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="K206" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L206" t="n">
         <v>0.99</v>
@@ -14436,13 +14436,13 @@
         <v>1</v>
       </c>
       <c r="O206" t="n">
-        <v>0.9934999999999999</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="P206" t="n">
         <v>1</v>
       </c>
       <c r="Q206" t="n">
-        <v>0.032</v>
+        <v>0.0299</v>
       </c>
       <c r="R206" t="n">
         <v>0.333</v>
@@ -14492,7 +14492,7 @@
         </is>
       </c>
       <c r="K207" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="L207" t="n">
         <v>0.99</v>
@@ -14504,13 +14504,13 @@
         <v>0.62</v>
       </c>
       <c r="O207" t="n">
-        <v>0.8694999999999999</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="P207" t="n">
         <v>2</v>
       </c>
       <c r="Q207" t="n">
-        <v>0.065</v>
+        <v>0.0583</v>
       </c>
       <c r="R207" t="n">
         <v>0.333</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="K208" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="L208" t="n">
         <v>0.99</v>
@@ -14572,13 +14572,13 @@
         <v>0.22</v>
       </c>
       <c r="O208" t="n">
-        <v>0.7065</v>
+        <v>0.7095</v>
       </c>
       <c r="P208" t="n">
         <v>3</v>
       </c>
       <c r="Q208" t="n">
-        <v>0.032</v>
+        <v>0.0299</v>
       </c>
       <c r="R208" t="n">
         <v>0.333</v>
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="K209" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L209" t="n">
         <v>0.74</v>
@@ -14640,7 +14640,7 @@
         <v>1</v>
       </c>
       <c r="O209" t="n">
-        <v>0.8550000000000001</v>
+        <v>0.858</v>
       </c>
       <c r="P209" t="n">
         <v>1</v>
@@ -14696,7 +14696,7 @@
         </is>
       </c>
       <c r="K210" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L210" t="n">
         <v>0.74</v>
@@ -14708,7 +14708,7 @@
         <v>0.22</v>
       </c>
       <c r="O210" t="n">
-        <v>0.62</v>
+        <v>0.623</v>
       </c>
       <c r="P210" t="n">
         <v>3</v>
@@ -14764,7 +14764,7 @@
         </is>
       </c>
       <c r="K211" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="L211" t="n">
         <v>0.77</v>
@@ -14776,7 +14776,7 @@
         <v>0.66</v>
       </c>
       <c r="O211" t="n">
-        <v>0.7805</v>
+        <v>0.7835</v>
       </c>
       <c r="P211" t="n">
         <v>2</v>
@@ -14850,7 +14850,7 @@
         <v>1</v>
       </c>
       <c r="Q212" t="n">
-        <v>0.048</v>
+        <v>0.0491</v>
       </c>
       <c r="R212" t="n">
         <v>0.156</v>
@@ -14912,13 +14912,13 @@
         <v>0.62</v>
       </c>
       <c r="O213" t="n">
-        <v>0.8909999999999999</v>
+        <v>0.891</v>
       </c>
       <c r="P213" t="n">
         <v>2</v>
       </c>
       <c r="Q213" t="n">
-        <v>0.0114</v>
+        <v>0.0126</v>
       </c>
       <c r="R213" t="n">
         <v>0.156</v>
@@ -14980,13 +14980,13 @@
         <v>0.41</v>
       </c>
       <c r="O214" t="n">
-        <v>0.7834999999999999</v>
+        <v>0.7835</v>
       </c>
       <c r="P214" t="n">
         <v>3</v>
       </c>
       <c r="Q214" t="n">
-        <v>0.0114</v>
+        <v>0.0126</v>
       </c>
       <c r="R214" t="n">
         <v>0.146</v>
@@ -15036,7 +15036,7 @@
         </is>
       </c>
       <c r="K215" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="L215" t="n">
         <v>0.36</v>
@@ -15048,7 +15048,7 @@
         <v>0.85</v>
       </c>
       <c r="O215" t="n">
-        <v>0.5685</v>
+        <v>0.5835</v>
       </c>
       <c r="P215" t="n">
         <v>1</v>
@@ -15104,7 +15104,7 @@
         </is>
       </c>
       <c r="K216" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="L216" t="n">
         <v>0.31</v>
@@ -15116,7 +15116,7 @@
         <v>0.39</v>
       </c>
       <c r="O216" t="n">
-        <v>0.4360000000000001</v>
+        <v>0.451</v>
       </c>
       <c r="P216" t="n">
         <v>2</v>
@@ -15172,7 +15172,7 @@
         </is>
       </c>
       <c r="K217" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="L217" t="n">
         <v>0.31</v>
@@ -15184,7 +15184,7 @@
         <v>0.34</v>
       </c>
       <c r="O217" t="n">
-        <v>0.4205</v>
+        <v>0.4355</v>
       </c>
       <c r="P217" t="n">
         <v>3</v>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night, when should I run the washing machine?</t>
+          <t>It's nearly 11 at night. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -15240,7 +15240,7 @@
         </is>
       </c>
       <c r="K218" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="L218" t="n">
         <v>0.96</v>
@@ -15252,13 +15252,13 @@
         <v>0.93</v>
       </c>
       <c r="O218" t="n">
-        <v>0.9255</v>
+        <v>0.9285</v>
       </c>
       <c r="P218" t="n">
         <v>1</v>
       </c>
       <c r="Q218" t="n">
-        <v>0.0391</v>
+        <v>0.0321</v>
       </c>
       <c r="R218" t="n">
         <v>0.41</v>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night, when should I run the washing machine?</t>
+          <t>It's nearly 11 at night. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -15320,13 +15320,13 @@
         <v>0.3</v>
       </c>
       <c r="O219" t="n">
-        <v>0.7689999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="P219" t="n">
         <v>3</v>
       </c>
       <c r="Q219" t="n">
-        <v>0.0391</v>
+        <v>0.0418</v>
       </c>
       <c r="R219" t="n">
         <v>0.437</v>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>It's nearly 11 at night, when should I run the washing machine?</t>
+          <t>It's nearly 11 at night. When should I run the washing machine?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -15376,7 +15376,7 @@
         </is>
       </c>
       <c r="K220" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="L220" t="n">
         <v>0.96</v>
@@ -15388,13 +15388,13 @@
         <v>0.43</v>
       </c>
       <c r="O220" t="n">
-        <v>0.7945</v>
+        <v>0.7975</v>
       </c>
       <c r="P220" t="n">
         <v>2</v>
       </c>
       <c r="Q220" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0828</v>
       </c>
       <c r="R220" t="n">
         <v>0.437</v>
@@ -15444,7 +15444,7 @@
         </is>
       </c>
       <c r="K221" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L221" t="n">
         <v>0.74</v>
@@ -15456,13 +15456,13 @@
         <v>0.85</v>
       </c>
       <c r="O221" t="n">
-        <v>0.8565</v>
+        <v>0.8685</v>
       </c>
       <c r="P221" t="n">
         <v>1</v>
       </c>
       <c r="Q221" t="n">
-        <v>0.0912</v>
+        <v>0.0727</v>
       </c>
       <c r="R221" t="n">
         <v>1.171</v>
@@ -15530,7 +15530,7 @@
         <v>2</v>
       </c>
       <c r="Q222" t="n">
-        <v>0.0912</v>
+        <v>0.1006</v>
       </c>
       <c r="R222" t="n">
         <v>1.249</v>
@@ -15598,7 +15598,7 @@
         <v>3</v>
       </c>
       <c r="Q223" t="n">
-        <v>0.0912</v>
+        <v>0.1006</v>
       </c>
       <c r="R223" t="n">
         <v>1.249</v>
@@ -15648,7 +15648,7 @@
         </is>
       </c>
       <c r="K224" t="n">
-        <v>0.38</v>
+        <v>0.51</v>
       </c>
       <c r="L224" t="n">
         <v>0.22</v>
@@ -15660,13 +15660,13 @@
         <v>1</v>
       </c>
       <c r="O224" t="n">
-        <v>0.541</v>
+        <v>0.58</v>
       </c>
       <c r="P224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q224" t="n">
-        <v>0.448</v>
+        <v>0.3916</v>
       </c>
       <c r="R224" t="n">
         <v>2.915</v>
@@ -15716,7 +15716,7 @@
         </is>
       </c>
       <c r="K225" t="n">
-        <v>0.75</v>
+        <v>0.51</v>
       </c>
       <c r="L225" t="n">
         <v>0.22</v>
@@ -15728,13 +15728,13 @@
         <v>0.82</v>
       </c>
       <c r="O225" t="n">
-        <v>0.603</v>
+        <v>0.531</v>
       </c>
       <c r="P225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q225" t="n">
-        <v>0.196</v>
+        <v>0.3916</v>
       </c>
       <c r="R225" t="n">
         <v>2.915</v>
@@ -15784,7 +15784,7 @@
         </is>
       </c>
       <c r="K226" t="n">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="L226" t="n">
         <v>0.22</v>
@@ -15796,13 +15796,13 @@
         <v>0.43</v>
       </c>
       <c r="O226" t="n">
-        <v>0.4545</v>
+        <v>0.4065</v>
       </c>
       <c r="P226" t="n">
         <v>3</v>
       </c>
       <c r="Q226" t="n">
-        <v>0.196</v>
+        <v>0.3356</v>
       </c>
       <c r="R226" t="n">
         <v>2.915</v>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -15852,7 +15852,7 @@
         </is>
       </c>
       <c r="K227" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="L227" t="n">
         <v>0.76</v>
@@ -15864,13 +15864,13 @@
         <v>1</v>
       </c>
       <c r="O227" t="n">
-        <v>0.847</v>
+        <v>0.85</v>
       </c>
       <c r="P227" t="n">
         <v>1</v>
       </c>
       <c r="Q227" t="n">
-        <v>0.1806</v>
+        <v>0.1914</v>
       </c>
       <c r="R227" t="n">
         <v>1.093</v>
@@ -15882,7 +15882,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="K228" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="L228" t="n">
         <v>0.76</v>
@@ -15932,13 +15932,13 @@
         <v>0.58</v>
       </c>
       <c r="O228" t="n">
-        <v>0.765</v>
+        <v>0.768</v>
       </c>
       <c r="P228" t="n">
         <v>2</v>
       </c>
       <c r="Q228" t="n">
-        <v>0.0924</v>
+        <v>0.0982</v>
       </c>
       <c r="R228" t="n">
         <v>1.093</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>It's late afternoon, just past 3, when should I run the dishwasher?</t>
+          <t>It's late afternoon, just past 3. When should I run the dishwasher?</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -15988,7 +15988,7 @@
         </is>
       </c>
       <c r="K229" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L229" t="n">
         <v>0.78</v>
@@ -16000,13 +16000,13 @@
         <v>0.34</v>
       </c>
       <c r="O229" t="n">
-        <v>0.718</v>
+        <v>0.73</v>
       </c>
       <c r="P229" t="n">
         <v>3</v>
       </c>
       <c r="Q229" t="n">
-        <v>0.0924</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="R229" t="n">
         <v>1.025</v>
@@ -16056,7 +16056,7 @@
         </is>
       </c>
       <c r="K230" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L230" t="n">
         <v>0.51</v>
@@ -16068,7 +16068,7 @@
         <v>1</v>
       </c>
       <c r="O230" t="n">
-        <v>0.7295</v>
+        <v>0.7385</v>
       </c>
       <c r="P230" t="n">
         <v>1</v>
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="K231" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L231" t="n">
         <v>0.51</v>
@@ -16136,7 +16136,7 @@
         <v>0.58</v>
       </c>
       <c r="O231" t="n">
-        <v>0.6084999999999999</v>
+        <v>0.6175</v>
       </c>
       <c r="P231" t="n">
         <v>2</v>
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="K232" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L232" t="n">
         <v>0.55</v>
@@ -16204,7 +16204,7 @@
         <v>0.29</v>
       </c>
       <c r="O232" t="n">
-        <v>0.551</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P232" t="n">
         <v>3</v>
@@ -16278,7 +16278,7 @@
         <v>1</v>
       </c>
       <c r="Q233" t="n">
-        <v>0.7585</v>
+        <v>0.8087</v>
       </c>
       <c r="R233" t="n">
         <v>4.268</v>
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="K234" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -16340,13 +16340,13 @@
         <v>0.49</v>
       </c>
       <c r="O234" t="n">
-        <v>0.3435</v>
+        <v>0.3465</v>
       </c>
       <c r="P234" t="n">
         <v>2</v>
       </c>
       <c r="Q234" t="n">
-        <v>0.3813</v>
+        <v>0.4085</v>
       </c>
       <c r="R234" t="n">
         <v>4.268</v>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="K235" t="n">
-        <v>0.48</v>
+        <v>0.62</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -16408,13 +16408,13 @@
         <v>0.15</v>
       </c>
       <c r="O235" t="n">
-        <v>0.1905</v>
+        <v>0.2325</v>
       </c>
       <c r="P235" t="n">
         <v>3</v>
       </c>
       <c r="Q235" t="n">
-        <v>0.3813</v>
+        <v>0.3135</v>
       </c>
       <c r="R235" t="n">
         <v>4.002</v>
@@ -16464,7 +16464,7 @@
         </is>
       </c>
       <c r="K236" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="L236" t="n">
         <v>0.82</v>
@@ -16476,13 +16476,13 @@
         <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>0.8889999999999999</v>
+        <v>0.901</v>
       </c>
       <c r="P236" t="n">
         <v>1</v>
       </c>
       <c r="Q236" t="n">
-        <v>0.136</v>
+        <v>0.1189</v>
       </c>
       <c r="R236" t="n">
         <v>0.885</v>
@@ -16532,7 +16532,7 @@
         </is>
       </c>
       <c r="K237" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L237" t="n">
         <v>0.84</v>
@@ -16544,13 +16544,13 @@
         <v>0.52</v>
       </c>
       <c r="O237" t="n">
-        <v>0.7489999999999999</v>
+        <v>0.734</v>
       </c>
       <c r="P237" t="n">
         <v>2</v>
       </c>
       <c r="Q237" t="n">
-        <v>0.0595</v>
+        <v>0.1019</v>
       </c>
       <c r="R237" t="n">
         <v>0.83</v>
@@ -16600,7 +16600,7 @@
         </is>
       </c>
       <c r="K238" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L238" t="n">
         <v>0.84</v>
@@ -16612,13 +16612,13 @@
         <v>0.39</v>
       </c>
       <c r="O238" t="n">
-        <v>0.6795</v>
+        <v>0.6645</v>
       </c>
       <c r="P238" t="n">
         <v>3</v>
       </c>
       <c r="Q238" t="n">
-        <v>0.0595</v>
+        <v>0.1019</v>
       </c>
       <c r="R238" t="n">
         <v>0.83</v>
@@ -16668,7 +16668,7 @@
         </is>
       </c>
       <c r="K239" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="L239" t="n">
         <v>0.43</v>
@@ -16680,13 +16680,13 @@
         <v>1</v>
       </c>
       <c r="O239" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.7105</v>
       </c>
       <c r="P239" t="n">
         <v>1</v>
       </c>
       <c r="Q239" t="n">
-        <v>0.147</v>
+        <v>0.2517</v>
       </c>
       <c r="R239" t="n">
         <v>2.186</v>
@@ -16736,7 +16736,7 @@
         </is>
       </c>
       <c r="K240" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="L240" t="n">
         <v>0.43</v>
@@ -16748,13 +16748,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="O240" t="n">
-        <v>0.5790000000000001</v>
+        <v>0.624</v>
       </c>
       <c r="P240" t="n">
         <v>2</v>
       </c>
       <c r="Q240" t="n">
-        <v>0.336</v>
+        <v>0.2517</v>
       </c>
       <c r="R240" t="n">
         <v>2.186</v>
@@ -16804,7 +16804,7 @@
         </is>
       </c>
       <c r="K241" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="L241" t="n">
         <v>0.47</v>
@@ -16816,13 +16816,13 @@
         <v>0.17</v>
       </c>
       <c r="O241" t="n">
-        <v>0.5319999999999999</v>
+        <v>0.496</v>
       </c>
       <c r="P241" t="n">
         <v>3</v>
       </c>
       <c r="Q241" t="n">
-        <v>0.147</v>
+        <v>0.2517</v>
       </c>
       <c r="R241" t="n">
         <v>2.05</v>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="K242" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="L242" t="n">
         <v>0.73</v>
@@ -16884,13 +16884,13 @@
         <v>1</v>
       </c>
       <c r="O242" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7645</v>
       </c>
       <c r="P242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q242" t="n">
-        <v>0.368</v>
+        <v>0.3766</v>
       </c>
       <c r="R242" t="n">
         <v>1.197</v>
@@ -16955,10 +16955,10 @@
         <v>0.7615</v>
       </c>
       <c r="P243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q243" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="R243" t="n">
         <v>1.122</v>
@@ -17020,13 +17020,13 @@
         <v>0.48</v>
       </c>
       <c r="O244" t="n">
-        <v>0.7264999999999999</v>
+        <v>0.7265</v>
       </c>
       <c r="P244" t="n">
         <v>3</v>
       </c>
       <c r="Q244" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="R244" t="n">
         <v>1.197</v>
@@ -17094,7 +17094,7 @@
         <v>1</v>
       </c>
       <c r="Q245" t="n">
-        <v>0.0243</v>
+        <v>0.0268</v>
       </c>
       <c r="R245" t="n">
         <v>0.333</v>
@@ -17144,7 +17144,7 @@
         </is>
       </c>
       <c r="K246" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="L246" t="n">
         <v>0.99</v>
@@ -17156,13 +17156,13 @@
         <v>0.67</v>
       </c>
       <c r="O246" t="n">
-        <v>0.87</v>
+        <v>0.873</v>
       </c>
       <c r="P246" t="n">
         <v>2</v>
       </c>
       <c r="Q246" t="n">
-        <v>0.1024</v>
+        <v>0.1048</v>
       </c>
       <c r="R246" t="n">
         <v>0.333</v>
@@ -17230,7 +17230,7 @@
         <v>3</v>
       </c>
       <c r="Q247" t="n">
-        <v>0.0243</v>
+        <v>0.0268</v>
       </c>
       <c r="R247" t="n">
         <v>0.312</v>
@@ -17298,7 +17298,7 @@
         <v>1</v>
       </c>
       <c r="Q248" t="n">
-        <v>0.2204</v>
+        <v>0.2431</v>
       </c>
       <c r="R248" t="n">
         <v>3.019</v>
@@ -17366,7 +17366,7 @@
         <v>3</v>
       </c>
       <c r="Q249" t="n">
-        <v>0.928</v>
+        <v>0.9497</v>
       </c>
       <c r="R249" t="n">
         <v>3.019</v>
@@ -17434,7 +17434,7 @@
         <v>2</v>
       </c>
       <c r="Q250" t="n">
-        <v>0.2204</v>
+        <v>0.2431</v>
       </c>
       <c r="R250" t="n">
         <v>3.019</v>
@@ -17484,7 +17484,7 @@
         </is>
       </c>
       <c r="K251" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="L251" t="n">
         <v>0.71</v>
@@ -17496,13 +17496,13 @@
         <v>1</v>
       </c>
       <c r="O251" t="n">
-        <v>0.7425</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q251" t="n">
-        <v>0.384</v>
+        <v>0.393</v>
       </c>
       <c r="R251" t="n">
         <v>1.249</v>
@@ -17564,13 +17564,13 @@
         <v>0.58</v>
       </c>
       <c r="O252" t="n">
-        <v>0.7474999999999999</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="P252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q252" t="n">
-        <v>0.0912</v>
+        <v>0.1006</v>
       </c>
       <c r="R252" t="n">
         <v>1.249</v>
@@ -17620,7 +17620,7 @@
         </is>
       </c>
       <c r="K253" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L253" t="n">
         <v>0.74</v>
@@ -17632,13 +17632,13 @@
         <v>0.15</v>
       </c>
       <c r="O253" t="n">
-        <v>0.6375</v>
+        <v>0.6495</v>
       </c>
       <c r="P253" t="n">
         <v>3</v>
       </c>
       <c r="Q253" t="n">
-        <v>0.0912</v>
+        <v>0.0727</v>
       </c>
       <c r="R253" t="n">
         <v>1.171</v>
@@ -17688,7 +17688,7 @@
         </is>
       </c>
       <c r="K254" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="L254" t="n">
         <v>0.96</v>
@@ -17700,13 +17700,13 @@
         <v>1</v>
       </c>
       <c r="O254" t="n">
-        <v>0.983</v>
+        <v>0.974</v>
       </c>
       <c r="P254" t="n">
         <v>1</v>
       </c>
       <c r="Q254" t="n">
-        <v>0.0294</v>
+        <v>0.0587</v>
       </c>
       <c r="R254" t="n">
         <v>0.437</v>
@@ -17756,7 +17756,7 @@
         </is>
       </c>
       <c r="K255" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L255" t="n">
         <v>0.96</v>
@@ -17768,13 +17768,13 @@
         <v>0.58</v>
       </c>
       <c r="O255" t="n">
-        <v>0.836</v>
+        <v>0.83</v>
       </c>
       <c r="P255" t="n">
         <v>2</v>
       </c>
       <c r="Q255" t="n">
-        <v>0.0294</v>
+        <v>0.0503</v>
       </c>
       <c r="R255" t="n">
         <v>0.41</v>
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="K256" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L256" t="n">
         <v>0.96</v>
@@ -17836,13 +17836,13 @@
         <v>0.3</v>
       </c>
       <c r="O256" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="P256" t="n">
         <v>3</v>
       </c>
       <c r="Q256" t="n">
-        <v>0.0294</v>
+        <v>0.0503</v>
       </c>
       <c r="R256" t="n">
         <v>0.437</v>
@@ -17910,7 +17910,7 @@
         <v>1</v>
       </c>
       <c r="Q257" t="n">
-        <v>0.2356</v>
+        <v>0.2598</v>
       </c>
       <c r="R257" t="n">
         <v>3.227</v>
@@ -17978,7 +17978,7 @@
         <v>3</v>
       </c>
       <c r="Q258" t="n">
-        <v>0.992</v>
+        <v>1.0152</v>
       </c>
       <c r="R258" t="n">
         <v>3.227</v>
@@ -18046,7 +18046,7 @@
         <v>2</v>
       </c>
       <c r="Q259" t="n">
-        <v>0.2356</v>
+        <v>0.2598</v>
       </c>
       <c r="R259" t="n">
         <v>3.026</v>
@@ -18114,7 +18114,7 @@
         <v>1</v>
       </c>
       <c r="Q260" t="n">
-        <v>0.0798</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R260" t="n">
         <v>1.093</v>
@@ -18164,7 +18164,7 @@
         </is>
       </c>
       <c r="K261" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="L261" t="n">
         <v>0.76</v>
@@ -18176,13 +18176,13 @@
         <v>0.62</v>
       </c>
       <c r="O261" t="n">
-        <v>0.6719999999999999</v>
+        <v>0.681</v>
       </c>
       <c r="P261" t="n">
         <v>3</v>
       </c>
       <c r="Q261" t="n">
-        <v>0.336</v>
+        <v>0.3438</v>
       </c>
       <c r="R261" t="n">
         <v>1.093</v>
@@ -18250,7 +18250,7 @@
         <v>2</v>
       </c>
       <c r="Q262" t="n">
-        <v>0.0798</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R262" t="n">
         <v>1.025</v>
@@ -18318,7 +18318,7 @@
         <v>1</v>
       </c>
       <c r="Q263" t="n">
-        <v>0.0266</v>
+        <v>0.0293</v>
       </c>
       <c r="R263" t="n">
         <v>0.364</v>
@@ -18386,7 +18386,7 @@
         <v>2</v>
       </c>
       <c r="Q264" t="n">
-        <v>0.0266</v>
+        <v>0.0293</v>
       </c>
       <c r="R264" t="n">
         <v>0.342</v>
@@ -18454,7 +18454,7 @@
         <v>3</v>
       </c>
       <c r="Q265" t="n">
-        <v>0.0266</v>
+        <v>0.0293</v>
       </c>
       <c r="R265" t="n">
         <v>0.364</v>
@@ -18522,7 +18522,7 @@
         <v>1</v>
       </c>
       <c r="Q266" t="n">
-        <v>0.2204</v>
+        <v>0.2431</v>
       </c>
       <c r="R266" t="n">
         <v>3.019</v>
@@ -18584,13 +18584,13 @@
         <v>0.67</v>
       </c>
       <c r="O267" t="n">
-        <v>0.3230000000000001</v>
+        <v>0.323</v>
       </c>
       <c r="P267" t="n">
         <v>3</v>
       </c>
       <c r="Q267" t="n">
-        <v>0.928</v>
+        <v>0.9497</v>
       </c>
       <c r="R267" t="n">
         <v>3.019</v>
@@ -18652,13 +18652,13 @@
         <v>0.27</v>
       </c>
       <c r="O268" t="n">
-        <v>0.3794999999999999</v>
+        <v>0.3795</v>
       </c>
       <c r="P268" t="n">
         <v>2</v>
       </c>
       <c r="Q268" t="n">
-        <v>0.2204</v>
+        <v>0.2431</v>
       </c>
       <c r="R268" t="n">
         <v>2.83</v>
@@ -18708,7 +18708,7 @@
         </is>
       </c>
       <c r="K269" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="L269" t="n">
         <v>0.7</v>
@@ -18720,13 +18720,13 @@
         <v>1</v>
       </c>
       <c r="O269" t="n">
-        <v>0.868</v>
+        <v>0.847</v>
       </c>
       <c r="P269" t="n">
         <v>1</v>
       </c>
       <c r="Q269" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1498</v>
       </c>
       <c r="R269" t="n">
         <v>1.301</v>
@@ -18776,7 +18776,7 @@
         </is>
       </c>
       <c r="K270" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="L270" t="n">
         <v>0.7</v>
@@ -18788,13 +18788,13 @@
         <v>0.58</v>
       </c>
       <c r="O270" t="n">
-        <v>0.696</v>
+        <v>0.726</v>
       </c>
       <c r="P270" t="n">
         <v>2</v>
       </c>
       <c r="Q270" t="n">
-        <v>0.2</v>
+        <v>0.1498</v>
       </c>
       <c r="R270" t="n">
         <v>1.301</v>
@@ -18844,7 +18844,7 @@
         </is>
       </c>
       <c r="K271" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="L271" t="n">
         <v>0.7</v>
@@ -18856,13 +18856,13 @@
         <v>0.23</v>
       </c>
       <c r="O271" t="n">
-        <v>0.6585</v>
+        <v>0.6375</v>
       </c>
       <c r="P271" t="n">
         <v>3</v>
       </c>
       <c r="Q271" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1498</v>
       </c>
       <c r="R271" t="n">
         <v>1.301</v>
@@ -18912,7 +18912,7 @@
         </is>
       </c>
       <c r="K272" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="L272" t="n">
         <v>0.96</v>
@@ -18924,13 +18924,13 @@
         <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>0.9679999999999999</v>
+        <v>0.977</v>
       </c>
       <c r="P272" t="n">
         <v>1</v>
       </c>
       <c r="Q272" t="n">
-        <v>0.0672</v>
+        <v>0.0503</v>
       </c>
       <c r="R272" t="n">
         <v>0.437</v>
@@ -18980,7 +18980,7 @@
         </is>
       </c>
       <c r="K273" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L273" t="n">
         <v>0.96</v>
@@ -18992,13 +18992,13 @@
         <v>0.62</v>
       </c>
       <c r="O273" t="n">
-        <v>0.874</v>
+        <v>0.868</v>
       </c>
       <c r="P273" t="n">
         <v>2</v>
       </c>
       <c r="Q273" t="n">
-        <v>0.0294</v>
+        <v>0.0503</v>
       </c>
       <c r="R273" t="n">
         <v>0.437</v>
@@ -19048,7 +19048,7 @@
         </is>
       </c>
       <c r="K274" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L274" t="n">
         <v>0.96</v>
@@ -19060,13 +19060,13 @@
         <v>0.15</v>
       </c>
       <c r="O274" t="n">
-        <v>0.7135</v>
+        <v>0.7075</v>
       </c>
       <c r="P274" t="n">
         <v>3</v>
       </c>
       <c r="Q274" t="n">
-        <v>0.0294</v>
+        <v>0.0503</v>
       </c>
       <c r="R274" t="n">
         <v>0.41</v>
@@ -19116,7 +19116,7 @@
         </is>
       </c>
       <c r="K275" t="n">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="L275" t="n">
         <v>0.12</v>
@@ -19128,13 +19128,13 @@
         <v>1</v>
       </c>
       <c r="O275" t="n">
-        <v>0.608</v>
+        <v>0.53</v>
       </c>
       <c r="P275" t="n">
         <v>1</v>
       </c>
       <c r="Q275" t="n">
-        <v>0.217</v>
+        <v>0.4336</v>
       </c>
       <c r="R275" t="n">
         <v>3.227</v>
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="K276" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="L276" t="n">
         <v>0.18</v>
@@ -19196,13 +19196,13 @@
         <v>0.57</v>
       </c>
       <c r="O276" t="n">
-        <v>0.4785</v>
+        <v>0.4245</v>
       </c>
       <c r="P276" t="n">
         <v>2</v>
       </c>
       <c r="Q276" t="n">
-        <v>0.217</v>
+        <v>0.3716</v>
       </c>
       <c r="R276" t="n">
         <v>3.026</v>
@@ -19252,7 +19252,7 @@
         </is>
       </c>
       <c r="K277" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="L277" t="n">
         <v>0.12</v>
@@ -19264,13 +19264,13 @@
         <v>0.3</v>
       </c>
       <c r="O277" t="n">
-        <v>0.397</v>
+        <v>0.343</v>
       </c>
       <c r="P277" t="n">
         <v>3</v>
       </c>
       <c r="Q277" t="n">
-        <v>0.217</v>
+        <v>0.3716</v>
       </c>
       <c r="R277" t="n">
         <v>3.227</v>
@@ -19332,13 +19332,13 @@
         <v>1</v>
       </c>
       <c r="O278" t="n">
-        <v>0.9189999999999999</v>
+        <v>0.919</v>
       </c>
       <c r="P278" t="n">
         <v>1</v>
       </c>
       <c r="Q278" t="n">
-        <v>0.0646</v>
+        <v>0.0712</v>
       </c>
       <c r="R278" t="n">
         <v>0.885</v>
@@ -19388,7 +19388,7 @@
         </is>
       </c>
       <c r="K279" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="L279" t="n">
         <v>0.82</v>
@@ -19400,13 +19400,13 @@
         <v>0.62</v>
       </c>
       <c r="O279" t="n">
-        <v>0.72</v>
+        <v>0.726</v>
       </c>
       <c r="P279" t="n">
         <v>3</v>
       </c>
       <c r="Q279" t="n">
-        <v>0.272</v>
+        <v>0.2783</v>
       </c>
       <c r="R279" t="n">
         <v>0.885</v>
@@ -19474,7 +19474,7 @@
         <v>2</v>
       </c>
       <c r="Q280" t="n">
-        <v>0.0646</v>
+        <v>0.0712</v>
       </c>
       <c r="R280" t="n">
         <v>0.83</v>
@@ -19524,7 +19524,7 @@
         </is>
       </c>
       <c r="K281" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="L281" t="n">
         <v>0.99</v>
@@ -19536,13 +19536,13 @@
         <v>1</v>
       </c>
       <c r="O281" t="n">
-        <v>0.9665</v>
+        <v>0.9695</v>
       </c>
       <c r="P281" t="n">
         <v>1</v>
       </c>
       <c r="Q281" t="n">
-        <v>0.096</v>
+        <v>0.0982</v>
       </c>
       <c r="R281" t="n">
         <v>0.312</v>
@@ -19610,7 +19610,7 @@
         <v>2</v>
       </c>
       <c r="Q282" t="n">
-        <v>0.0228</v>
+        <v>0.0251</v>
       </c>
       <c r="R282" t="n">
         <v>0.312</v>
@@ -19672,13 +19672,13 @@
         <v>0.48</v>
       </c>
       <c r="O283" t="n">
-        <v>0.8159999999999998</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="P283" t="n">
         <v>3</v>
       </c>
       <c r="Q283" t="n">
-        <v>0.0228</v>
+        <v>0.0251</v>
       </c>
       <c r="R283" t="n">
         <v>0.293</v>
@@ -19728,7 +19728,7 @@
         </is>
       </c>
       <c r="K284" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="L284" t="n">
         <v>0.22</v>
@@ -19740,13 +19740,13 @@
         <v>1</v>
       </c>
       <c r="O284" t="n">
-        <v>0.646</v>
+        <v>0.643</v>
       </c>
       <c r="P284" t="n">
         <v>1</v>
       </c>
       <c r="Q284" t="n">
-        <v>0.2128</v>
+        <v>0.2347</v>
       </c>
       <c r="R284" t="n">
         <v>2.915</v>
@@ -19796,7 +19796,7 @@
         </is>
       </c>
       <c r="K285" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="L285" t="n">
         <v>0.27</v>
@@ -19808,13 +19808,13 @@
         <v>0.62</v>
       </c>
       <c r="O285" t="n">
-        <v>0.5305</v>
+        <v>0.5275</v>
       </c>
       <c r="P285" t="n">
         <v>2</v>
       </c>
       <c r="Q285" t="n">
-        <v>0.2128</v>
+        <v>0.2347</v>
       </c>
       <c r="R285" t="n">
         <v>2.733</v>
@@ -19864,7 +19864,7 @@
         </is>
       </c>
       <c r="K286" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="L286" t="n">
         <v>0.22</v>
@@ -19876,13 +19876,13 @@
         <v>0.39</v>
       </c>
       <c r="O286" t="n">
-        <v>0.4645</v>
+        <v>0.4615</v>
       </c>
       <c r="P286" t="n">
         <v>3</v>
       </c>
       <c r="Q286" t="n">
-        <v>0.2128</v>
+        <v>0.2347</v>
       </c>
       <c r="R286" t="n">
         <v>2.915</v>
@@ -19932,7 +19932,7 @@
         </is>
       </c>
       <c r="K287" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="L287" t="n">
         <v>0.74</v>
@@ -19944,13 +19944,13 @@
         <v>1</v>
       </c>
       <c r="O287" t="n">
-        <v>0.8850000000000001</v>
+        <v>0.867</v>
       </c>
       <c r="P287" t="n">
         <v>1</v>
       </c>
       <c r="Q287" t="n">
-        <v>0.077</v>
+        <v>0.1319</v>
       </c>
       <c r="R287" t="n">
         <v>1.145</v>
@@ -20000,7 +20000,7 @@
         </is>
       </c>
       <c r="K288" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="L288" t="n">
         <v>0.74</v>
@@ -20012,13 +20012,13 @@
         <v>0.72</v>
       </c>
       <c r="O288" t="n">
-        <v>0.765</v>
+        <v>0.789</v>
       </c>
       <c r="P288" t="n">
         <v>2</v>
       </c>
       <c r="Q288" t="n">
-        <v>0.176</v>
+        <v>0.1319</v>
       </c>
       <c r="R288" t="n">
         <v>1.145</v>
@@ -20068,7 +20068,7 @@
         </is>
       </c>
       <c r="K289" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="L289" t="n">
         <v>0.74</v>
@@ -20080,13 +20080,13 @@
         <v>0.27</v>
       </c>
       <c r="O289" t="n">
-        <v>0.6855</v>
+        <v>0.6675</v>
       </c>
       <c r="P289" t="n">
         <v>3</v>
       </c>
       <c r="Q289" t="n">
-        <v>0.077</v>
+        <v>0.1319</v>
       </c>
       <c r="R289" t="n">
         <v>1.145</v>
@@ -20098,7 +20098,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="K290" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L290" t="n">
         <v>0.28</v>
@@ -20148,7 +20148,7 @@
         <v>1</v>
       </c>
       <c r="O290" t="n">
-        <v>0.601</v>
+        <v>0.616</v>
       </c>
       <c r="P290" t="n">
         <v>1</v>
@@ -20166,7 +20166,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -20204,7 +20204,7 @@
         </is>
       </c>
       <c r="K291" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L291" t="n">
         <v>0.28</v>
@@ -20216,7 +20216,7 @@
         <v>0.6</v>
       </c>
       <c r="O291" t="n">
-        <v>0.487</v>
+        <v>0.502</v>
       </c>
       <c r="P291" t="n">
         <v>2</v>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>It's around 2 in the afternoon, when should I run the dryer?</t>
+          <t>It's around 2 in the afternoon. When should I run the dryer?</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="K292" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L292" t="n">
         <v>0.28</v>
@@ -20284,7 +20284,7 @@
         <v>0.31</v>
       </c>
       <c r="O292" t="n">
-        <v>0.3655</v>
+        <v>0.3805</v>
       </c>
       <c r="P292" t="n">
         <v>3</v>
@@ -20340,7 +20340,7 @@
         </is>
       </c>
       <c r="K293" t="n">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="L293" t="n">
         <v>0.5600000000000001</v>
@@ -20352,13 +20352,13 @@
         <v>1</v>
       </c>
       <c r="O293" t="n">
-        <v>0.804</v>
+        <v>0.762</v>
       </c>
       <c r="P293" t="n">
         <v>1</v>
       </c>
       <c r="Q293" t="n">
-        <v>0.119</v>
+        <v>0.2378</v>
       </c>
       <c r="R293" t="n">
         <v>1.77</v>
@@ -20408,7 +20408,7 @@
         </is>
       </c>
       <c r="K294" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="L294" t="n">
         <v>0.5600000000000001</v>
@@ -20420,13 +20420,13 @@
         <v>0.35</v>
       </c>
       <c r="O294" t="n">
-        <v>0.6105</v>
+        <v>0.5805</v>
       </c>
       <c r="P294" t="n">
         <v>3</v>
       </c>
       <c r="Q294" t="n">
-        <v>0.119</v>
+        <v>0.2038</v>
       </c>
       <c r="R294" t="n">
         <v>1.77</v>
@@ -20476,7 +20476,7 @@
         </is>
       </c>
       <c r="K295" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="L295" t="n">
         <v>0.5600000000000001</v>
@@ -20488,13 +20488,13 @@
         <v>0.57</v>
       </c>
       <c r="O295" t="n">
-        <v>0.6955000000000001</v>
+        <v>0.6655</v>
       </c>
       <c r="P295" t="n">
         <v>2</v>
       </c>
       <c r="Q295" t="n">
-        <v>0.119</v>
+        <v>0.2038</v>
       </c>
       <c r="R295" t="n">
         <v>1.77</v>
@@ -20540,11 +20540,11 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>6pm</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="K296" t="n">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="L296" t="n">
         <v>0.34</v>
@@ -20556,13 +20556,13 @@
         <v>1</v>
       </c>
       <c r="O296" t="n">
-        <v>0.7060000000000001</v>
+        <v>0.646</v>
       </c>
       <c r="P296" t="n">
         <v>1</v>
       </c>
       <c r="Q296" t="n">
-        <v>0.168</v>
+        <v>0.3357</v>
       </c>
       <c r="R296" t="n">
         <v>2.498</v>
@@ -20608,11 +20608,11 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>10pm</t>
+          <t>10:00 PM</t>
         </is>
       </c>
       <c r="K297" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="L297" t="n">
         <v>0.34</v>
@@ -20624,13 +20624,13 @@
         <v>0.57</v>
       </c>
       <c r="O297" t="n">
-        <v>0.5555</v>
+        <v>0.5135</v>
       </c>
       <c r="P297" t="n">
         <v>2</v>
       </c>
       <c r="Q297" t="n">
-        <v>0.168</v>
+        <v>0.2877</v>
       </c>
       <c r="R297" t="n">
         <v>2.498</v>
@@ -20676,11 +20676,11 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>6am</t>
+          <t>6:00 AM</t>
         </is>
       </c>
       <c r="K298" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="L298" t="n">
         <v>0.39</v>
@@ -20692,13 +20692,13 @@
         <v>0.25</v>
       </c>
       <c r="O298" t="n">
-        <v>0.4349999999999999</v>
+        <v>0.393</v>
       </c>
       <c r="P298" t="n">
         <v>3</v>
       </c>
       <c r="Q298" t="n">
-        <v>0.168</v>
+        <v>0.2877</v>
       </c>
       <c r="R298" t="n">
         <v>2.342</v>
@@ -20744,7 +20744,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>8am</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="K299" t="n">
@@ -20766,7 +20766,7 @@
         <v>1</v>
       </c>
       <c r="Q299" t="n">
-        <v>0.0798</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R299" t="n">
         <v>1.093</v>
@@ -20812,11 +20812,11 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>2pm</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="K300" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="L300" t="n">
         <v>0.76</v>
@@ -20828,13 +20828,13 @@
         <v>0.58</v>
       </c>
       <c r="O300" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.669</v>
       </c>
       <c r="P300" t="n">
         <v>3</v>
       </c>
       <c r="Q300" t="n">
-        <v>0.336</v>
+        <v>0.3438</v>
       </c>
       <c r="R300" t="n">
         <v>1.093</v>
@@ -20880,7 +20880,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>11pm</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="K301" t="n">
@@ -20896,13 +20896,13 @@
         <v>0.29</v>
       </c>
       <c r="O301" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.7065</v>
       </c>
       <c r="P301" t="n">
         <v>2</v>
       </c>
       <c r="Q301" t="n">
-        <v>0.0798</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="R301" t="n">
         <v>1.025</v>
